--- a/股票组合风险分析_参考答案.xlsx
+++ b/股票组合风险分析_参考答案.xlsx
@@ -24,9 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="132">
   <si>
-    <t>模拟股票月度行情（数据已完整提供，无需外部检索）</t>
+    <t>模拟股票月度行情</t>
   </si>
   <si>
     <t>日期</t>
@@ -209,10 +209,7 @@
     <t>增长反弹</t>
   </si>
   <si>
-    <t>股票组合收益与风险分析</t>
-  </si>
-  <si>
-    <t>蓝色单元格为公式结果；所有收益率、风险指标与贡献值均应保持公式联动。</t>
+    <t>股票组合分析</t>
   </si>
   <si>
     <t>最新价</t>
@@ -248,7 +245,7 @@
     <t>加权Beta贡献</t>
   </si>
   <si>
-    <t>月度VaR贡献</t>
+    <t>95%单尾月度VaR贡献</t>
   </si>
   <si>
     <t>配置判断</t>
@@ -299,10 +296,7 @@
     <t>组合回撤</t>
   </si>
   <si>
-    <t>股票组合情景压力测试</t>
-  </si>
-  <si>
-    <t>按行业冲击映射至每只股票，计算持仓市值和情景损益；负值代表亏损。</t>
+    <t>压力测试</t>
   </si>
   <si>
     <t>情景</t>
@@ -326,19 +320,19 @@
     <t>风险判断</t>
   </si>
   <si>
-    <t>股票组合投资仪表盘</t>
+    <t>投资仪表盘</t>
   </si>
   <si>
     <t>95%单月VaR率</t>
   </si>
   <si>
-    <t>风险贡献最高的 5 只股票</t>
+    <t>VaR贡献前五持仓</t>
   </si>
   <si>
     <t>排名</t>
   </si>
   <si>
-    <t>六行业协方差风险归因</t>
+    <t>行业风险归因</t>
   </si>
   <si>
     <t>月末</t>
@@ -380,7 +374,7 @@
     <t>最大风险贡献行业</t>
   </si>
   <si>
-    <t>单步前瞻风险回测（前12个月预测下一月）</t>
+    <t>风险回测</t>
   </si>
   <si>
     <t>检验月末</t>
@@ -438,7 +432,7 @@
     <numFmt numFmtId="166" formatCode="¥#,##0;[Red]-¥#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,8 +442,8 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -457,37 +451,28 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,43 +481,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FFE7E6E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFEDEDED"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
+        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF2F8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFF7E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,10 +533,8 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -582,23 +547,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1536,7 +1501,7 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1599,8 +1564,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -1914,9 +1879,10 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="7" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1930,7 +1896,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="26" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -8592,8 +8558,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" customWidth="1"/>
     <col min="4" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8606,7 +8572,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="26" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
@@ -8912,14 +8878,22 @@
   <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26" customHeight="1">
+    <row r="1" spans="1:17" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
@@ -8940,28 +8914,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-    </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" ht="46" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -8972,46 +8925,46 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>55</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -9024,11 +8977,11 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>'原始行情'!E279</f>
         <v>20.5</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>'原始行情'!E3</f>
         <v>18.0</v>
       </c>
@@ -9044,7 +8997,7 @@
         <f>STDEV.S('月度收益'!B$2:B$24)*SQRT(12)</f>
         <v>0.1456956289744867</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>SLOPE('月度收益'!B$2:B$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.2767811493183567</v>
       </c>
@@ -9068,15 +9021,15 @@
         <f>M6*G6</f>
         <v>0.007508190658720038</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="12">
         <f>M6*I6</f>
         <v>0.12767811493183567</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="13">
         <f>M6*'参数设置'!$B$3*'参数设置'!$B$7*H6/SQRT(12)</f>
         <v>69186.57022522126</v>
       </c>
-      <c r="Q6" s="4" t="str">
+      <c r="Q6" s="14" t="str">
         <f>IF(AND(K6&gt;1.5%,I6&lt;1.15),"增配观察",IF(K6&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9091,11 +9044,11 @@
       <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>'原始行情'!E280</f>
         <v>25.96</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f>'原始行情'!E4</f>
         <v>21.15</v>
       </c>
@@ -9111,7 +9064,7 @@
         <f>STDEV.S('月度收益'!C$2:C$24)*SQRT(12)</f>
         <v>0.12055472227851159</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f>SLOPE('月度收益'!C$2:C$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.9053807458088171</v>
       </c>
@@ -9135,15 +9088,15 @@
         <f>M7*G7</f>
         <v>0.010594724229992376</v>
       </c>
-      <c r="O7" s="13">
+      <c r="O7" s="12">
         <f>M7*I7</f>
         <v>0.08148426712279354</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="13">
         <f>M7*'参数设置'!$B$3*'参数设置'!$B$7*H7/SQRT(12)</f>
         <v>51523.103581428535</v>
       </c>
-      <c r="Q7" s="4" t="str">
+      <c r="Q7" s="14" t="str">
         <f>IF(AND(K7&gt;1.5%,I7&lt;1.15),"增配观察",IF(K7&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9158,11 +9111,11 @@
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>'原始行情'!E281</f>
         <v>30.48</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f>'原始行情'!E5</f>
         <v>24.3</v>
       </c>
@@ -9178,7 +9131,7 @@
         <f>STDEV.S('月度收益'!D$2:D$24)*SQRT(12)</f>
         <v>0.13469917550784388</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>SLOPE('月度收益'!D$2:D$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.0547850693234158</v>
       </c>
@@ -9202,15 +9155,15 @@
         <f>M8*G8</f>
         <v>0.013012721958356212</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="12">
         <f>M8*I8</f>
         <v>0.10547850693234158</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="13">
         <f>M8*'参数设置'!$B$3*'参数设置'!$B$7*H8/SQRT(12)</f>
         <v>63964.67780913862</v>
       </c>
-      <c r="Q8" s="4" t="str">
+      <c r="Q8" s="14" t="str">
         <f>IF(AND(K8&gt;1.5%,I8&lt;1.15),"增配观察",IF(K8&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9225,11 +9178,11 @@
       <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>'原始行情'!E282</f>
         <v>35.75</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f>'原始行情'!E6</f>
         <v>27.45</v>
       </c>
@@ -9245,7 +9198,7 @@
         <f>STDEV.S('月度收益'!E$2:E$24)*SQRT(12)</f>
         <v>0.14692905527527328</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>SLOPE('月度收益'!E$2:E$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.1958995667562984</v>
       </c>
@@ -9269,15 +9222,15 @@
         <f>M9*G9</f>
         <v>0.012187348246355168</v>
       </c>
-      <c r="O9" s="13">
+      <c r="O9" s="12">
         <f>M9*I9</f>
         <v>0.09567196534050387</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="13">
         <f>M9*'参数设置'!$B$3*'参数设置'!$B$7*H9/SQRT(12)</f>
         <v>55817.83048664134</v>
       </c>
-      <c r="Q9" s="4" t="str">
+      <c r="Q9" s="14" t="str">
         <f>IF(AND(K9&gt;1.5%,I9&lt;1.15),"增配观察",IF(K9&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9292,11 +9245,11 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f>'原始行情'!E283</f>
         <v>37.66</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <f>'原始行情'!E7</f>
         <v>30.6</v>
       </c>
@@ -9312,7 +9265,7 @@
         <f>STDEV.S('月度收益'!F$2:F$24)*SQRT(12)</f>
         <v>0.15235002686894922</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f>SLOPE('月度收益'!F$2:F$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.2477179581923739</v>
       </c>
@@ -9336,15 +9289,15 @@
         <f>M10*G10</f>
         <v>0.010690850619391231</v>
       </c>
-      <c r="O10" s="13">
+      <c r="O10" s="12">
         <f>M10*I10</f>
         <v>0.11229461623731364</v>
       </c>
-      <c r="P10" s="14">
+      <c r="P10" s="13">
         <f>M10*'参数设置'!$B$3*'参数设置'!$B$7*H10/SQRT(12)</f>
         <v>65111.89330989353</v>
       </c>
-      <c r="Q10" s="4" t="str">
+      <c r="Q10" s="14" t="str">
         <f>IF(AND(K10&gt;1.5%,I10&lt;1.15),"增配观察",IF(K10&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9359,11 +9312,11 @@
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>'原始行情'!E284</f>
         <v>42.79</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f>'原始行情'!E8</f>
         <v>33.75</v>
       </c>
@@ -9379,7 +9332,7 @@
         <f>STDEV.S('月度收益'!G$2:G$24)*SQRT(12)</f>
         <v>0.14193508207629768</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f>SLOPE('月度收益'!G$2:G$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.146751788731645</v>
       </c>
@@ -9403,15 +9356,15 @@
         <f>M11*G11</f>
         <v>0.009525183853490203</v>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="12">
         <f>M11*I11</f>
         <v>0.08027262521121516</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="13">
         <f>M11*'参数设置'!$B$3*'参数设置'!$B$7*H11/SQRT(12)</f>
         <v>47180.55795379937</v>
       </c>
-      <c r="Q11" s="4" t="str">
+      <c r="Q11" s="14" t="str">
         <f>IF(AND(K11&gt;1.5%,I11&lt;1.15),"增配观察",IF(K11&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9426,11 +9379,11 @@
       <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f>'原始行情'!E285</f>
         <v>45.63</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <f>'原始行情'!E9</f>
         <v>36.9</v>
       </c>
@@ -9446,7 +9399,7 @@
         <f>STDEV.S('月度收益'!H$2:H$24)*SQRT(12)</f>
         <v>0.10340249541263921</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f>SLOPE('月度收益'!H$2:H$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.7096873510466656</v>
       </c>
@@ -9470,15 +9423,15 @@
         <f>M12*G12</f>
         <v>0.010927005514994382</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="12">
         <f>M12*I12</f>
         <v>0.0638718615941999</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="13">
         <f>M12*'参数设置'!$B$3*'参数设置'!$B$7*H12/SQRT(12)</f>
         <v>44192.5242000514</v>
       </c>
-      <c r="Q12" s="4" t="str">
+      <c r="Q12" s="14" t="str">
         <f>IF(AND(K12&gt;1.5%,I12&lt;1.15),"增配观察",IF(K12&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9493,11 +9446,11 @@
       <c r="C13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>'原始行情'!E286</f>
         <v>50.69</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f>'原始行情'!E10</f>
         <v>40.05</v>
       </c>
@@ -9513,7 +9466,7 @@
         <f>STDEV.S('月度收益'!I$2:I$24)*SQRT(12)</f>
         <v>0.09893832677334906</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>SLOPE('月度收益'!I$2:I$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.6635655624507926</v>
       </c>
@@ -9537,15 +9490,15 @@
         <f>M13*G13</f>
         <v>0.01079635727270846</v>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="12">
         <f>M13*I13</f>
         <v>0.05308524499606341</v>
       </c>
-      <c r="P13" s="14">
+      <c r="P13" s="13">
         <f>M13*'参数设置'!$B$3*'参数设置'!$B$7*H13/SQRT(12)</f>
         <v>37586.32179401287</v>
       </c>
-      <c r="Q13" s="4" t="str">
+      <c r="Q13" s="14" t="str">
         <f>IF(AND(K13&gt;1.5%,I13&lt;1.15),"增配观察",IF(K13&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9560,11 +9513,11 @@
       <c r="C14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f>'原始行情'!E287</f>
         <v>52.34</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <f>'原始行情'!E11</f>
         <v>43.2</v>
       </c>
@@ -9580,7 +9533,7 @@
         <f>STDEV.S('月度收益'!J$2:J$24)*SQRT(12)</f>
         <v>0.12796348354711454</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <f>SLOPE('月度收益'!J$2:J$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.9891348209809542</v>
       </c>
@@ -9604,15 +9557,15 @@
         <f>M14*G14</f>
         <v>0.008768784455502825</v>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="12">
         <f>M14*I14</f>
         <v>0.07913078567847634</v>
       </c>
-      <c r="P14" s="14">
+      <c r="P14" s="13">
         <f>M14*'参数设置'!$B$3*'参数设置'!$B$7*H14/SQRT(12)</f>
         <v>48612.87660041869</v>
       </c>
-      <c r="Q14" s="4" t="str">
+      <c r="Q14" s="14" t="str">
         <f>IF(AND(K14&gt;1.5%,I14&lt;1.15),"增配观察",IF(K14&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9627,11 +9580,11 @@
       <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <f>'原始行情'!E288</f>
         <v>57.74</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f>'原始行情'!E12</f>
         <v>46.35</v>
       </c>
@@ -9647,7 +9600,7 @@
         <f>STDEV.S('月度收益'!K$2:K$24)*SQRT(12)</f>
         <v>0.12549312207531008</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f>SLOPE('月度收益'!K$2:K$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.9834282584451242</v>
       </c>
@@ -9671,15 +9624,15 @@
         <f>M15*G15</f>
         <v>0.00880655884105434</v>
       </c>
-      <c r="O15" s="13">
+      <c r="O15" s="12">
         <f>M15*I15</f>
         <v>0.0688399780911587</v>
       </c>
-      <c r="P15" s="14">
+      <c r="P15" s="13">
         <f>M15*'参数设置'!$B$3*'参数设置'!$B$7*H15/SQRT(12)</f>
         <v>41715.095607544165</v>
       </c>
-      <c r="Q15" s="4" t="str">
+      <c r="Q15" s="14" t="str">
         <f>IF(AND(K15&gt;1.5%,I15&lt;1.15),"增配观察",IF(K15&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9694,11 +9647,11 @@
       <c r="C16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <f>'原始行情'!E289</f>
         <v>65.33</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f>'原始行情'!E13</f>
         <v>49.5</v>
       </c>
@@ -9714,7 +9667,7 @@
         <f>STDEV.S('月度收益'!L$2:L$24)*SQRT(12)</f>
         <v>0.14278900532998365</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f>SLOPE('月度收益'!L$2:L$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.1553402857334645</v>
       </c>
@@ -9738,15 +9691,15 @@
         <f>M16*G16</f>
         <v>0.012816430514175609</v>
       </c>
-      <c r="O16" s="13">
+      <c r="O16" s="12">
         <f>M16*I16</f>
         <v>0.09242722285867716</v>
       </c>
-      <c r="P16" s="14">
+      <c r="P16" s="13">
         <f>M16*'参数设置'!$B$3*'参数设置'!$B$7*H16/SQRT(12)</f>
         <v>54245.04009729691</v>
       </c>
-      <c r="Q16" s="4" t="str">
+      <c r="Q16" s="14" t="str">
         <f>IF(AND(K16&gt;1.5%,I16&lt;1.15),"增配观察",IF(K16&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9761,11 +9714,11 @@
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <f>'原始行情'!E290</f>
         <v>71.78</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <f>'原始行情'!E14</f>
         <v>52.65</v>
       </c>
@@ -9781,7 +9734,7 @@
         <f>STDEV.S('月度收益'!M$2:M$24)*SQRT(12)</f>
         <v>0.1632534986219611</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f>SLOPE('月度收益'!M$2:M$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.3806784934734606</v>
       </c>
@@ -9805,27 +9758,27 @@
         <f>M17*G17</f>
         <v>0.012604765174439217</v>
       </c>
-      <c r="O17" s="13">
+      <c r="O17" s="12">
         <f>M17*I17</f>
         <v>0.09664749454314225</v>
       </c>
-      <c r="P17" s="14">
+      <c r="P17" s="13">
         <f>M17*'参数设置'!$B$3*'参数设置'!$B$7*H17/SQRT(12)</f>
         <v>54267.000379465695</v>
       </c>
-      <c r="Q17" s="4" t="str">
+      <c r="Q17" s="14" t="str">
         <f>IF(AND(K17&gt;1.5%,I17&lt;1.15),"增配观察",IF(K17&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11">
         <f>SUM(M6:M17)</f>
@@ -9834,7 +9787,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11">
         <f>'月度收益'!P24^(12/23)-1</f>
@@ -9843,7 +9796,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11">
         <f>STDEV.S('月度收益'!O2:O24)*SQRT(12)</f>
@@ -9852,34 +9805,34 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="13">
+        <v>79</v>
+      </c>
+      <c r="B24" s="12">
         <f>SUM(O6:O17)</f>
         <v>1.0568826835377212</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="14">
+        <v>80</v>
+      </c>
+      <c r="B25" s="13">
         <f>'参数设置'!B3*'参数设置'!B7*STDEV.S('月度收益'!O2:O24)</f>
         <v>543993.0944790144</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="13">
+        <v>81</v>
+      </c>
+      <c r="B26" s="12">
         <f>(B22-'参数设置'!B4)/B23</f>
         <v>0.9482416368361284</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="11">
         <f>MIN('月度收益'!R2:R24)</f>
@@ -9888,7 +9841,7 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" s="11">
         <f>('原始行情'!G279/'原始行情'!G3)^(12/23)-1</f>
@@ -9896,9 +9849,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="K6:K17">
     <cfRule type="colorScale" priority="1">
@@ -9931,12 +9883,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="18" width="13.7109375" customWidth="1"/>
+    <col min="2" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>8</v>
@@ -9975,19 +9929,19 @@
         <v>36</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -10050,11 +10004,11 @@
         <f>SUMPRODUCT(B2:M2,'参数设置'!$E$4:$E$15)</f>
         <v>0.037134327253655015</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="12">
         <f>1+O2</f>
         <v>1.037134327253655</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="12">
         <f>1+N2</f>
         <v>1.02931</v>
       </c>
@@ -10123,11 +10077,11 @@
         <f>SUMPRODUCT(B3:M3,'参数设置'!$E$4:$E$15)</f>
         <v>0.03141661170603247</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="12">
         <f>P2*(1+O3)</f>
         <v>1.0697175736999802</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="12">
         <f>Q2*(1+N3)</f>
         <v>1.0568099999999998</v>
       </c>
@@ -10196,11 +10150,11 @@
         <f>SUMPRODUCT(B4:M4,'参数设置'!$E$4:$E$15)</f>
         <v>0.01493417133421877</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="12">
         <f>P3*(1+O4)</f>
         <v>1.0856929192248406</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="12">
         <f>Q3*(1+N4)</f>
         <v>1.0702599999999998</v>
       </c>
@@ -10269,11 +10223,11 @@
         <f>SUMPRODUCT(B5:M5,'参数设置'!$E$4:$E$15)</f>
         <v>-0.0014502137279292998</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="12">
         <f>P4*(1+O5)</f>
         <v>1.0841184324490651</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="12">
         <f>Q4*(1+N5)</f>
         <v>1.0670299999999997</v>
       </c>
@@ -10342,11 +10296,11 @@
         <f>SUMPRODUCT(B6:M6,'参数设置'!$E$4:$E$15)</f>
         <v>-0.00313782368107464</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="12">
         <f>P5*(1+O6)</f>
         <v>1.0807166599586369</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="12">
         <f>Q5*(1+N6)</f>
         <v>1.0560499999999997</v>
       </c>
@@ -10415,11 +10369,11 @@
         <f>SUMPRODUCT(B7:M7,'参数设置'!$E$4:$E$15)</f>
         <v>0.0004933093934501105</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="12">
         <f>P6*(1+O7)</f>
         <v>1.0812497876386524</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="Q7" s="12">
         <f>Q6*(1+N7)</f>
         <v>1.05168</v>
       </c>
@@ -10488,11 +10442,11 @@
         <f>SUMPRODUCT(B8:M8,'参数设置'!$E$4:$E$15)</f>
         <v>-0.0393434814115395</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="12">
         <f>P7*(1+O8)</f>
         <v>1.03870965671746</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="12">
         <f>Q7*(1+N8)</f>
         <v>1.00653</v>
       </c>
@@ -10561,11 +10515,11 @@
         <f>SUMPRODUCT(B9:M9,'参数设置'!$E$4:$E$15)</f>
         <v>0.03469283927183994</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="12">
         <f>P8*(1+O9)</f>
         <v>1.074745443888067</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="12">
         <f>Q8*(1+N9)</f>
         <v>1.03531</v>
       </c>
@@ -10634,11 +10588,11 @@
         <f>SUMPRODUCT(B10:M10,'参数设置'!$E$4:$E$15)</f>
         <v>0.03966771802949588</v>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="12">
         <f>P9*(1+O10)</f>
         <v>1.1173781431097043</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="12">
         <f>Q9*(1+N10)</f>
         <v>1.0714299999999999</v>
       </c>
@@ -10707,11 +10661,11 @@
         <f>SUMPRODUCT(B11:M11,'参数设置'!$E$4:$E$15)</f>
         <v>0.07641388070651696</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="12">
         <f>P10*(1+O11)</f>
         <v>1.2027613432413586</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="12">
         <f>Q10*(1+N11)</f>
         <v>1.1472599999999997</v>
       </c>
@@ -10780,11 +10734,11 @@
         <f>SUMPRODUCT(B12:M12,'参数设置'!$E$4:$E$15)</f>
         <v>0.011142814611335518</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="12">
         <f>P11*(1+O12)</f>
         <v>1.216163489910778</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="Q12" s="12">
         <f>Q11*(1+N12)</f>
         <v>1.1525199999999998</v>
       </c>
@@ -10853,11 +10807,11 @@
         <f>SUMPRODUCT(B13:M13,'参数设置'!$E$4:$E$15)</f>
         <v>-0.012866339018591872</v>
       </c>
-      <c r="P13" s="13">
+      <c r="P13" s="12">
         <f>P12*(1+O13)</f>
         <v>1.2005159181475522</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13" s="12">
         <f>Q12*(1+N13)</f>
         <v>1.1314</v>
       </c>
@@ -10926,11 +10880,11 @@
         <f>SUMPRODUCT(B14:M14,'参数设置'!$E$4:$E$15)</f>
         <v>-0.02857961496630279</v>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="12">
         <f>P13*(1+O14)</f>
         <v>1.1662056354459778</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="Q14" s="12">
         <f>Q13*(1+N14)</f>
         <v>1.09601</v>
       </c>
@@ -10999,11 +10953,11 @@
         <f>SUMPRODUCT(B15:M15,'参数设置'!$E$4:$E$15)</f>
         <v>-0.02817391571200374</v>
       </c>
-      <c r="P15" s="13">
+      <c r="P15" s="12">
         <f>P14*(1+O15)</f>
         <v>1.133349056170059</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="Q15" s="12">
         <f>Q14*(1+N15)</f>
         <v>1.0658299999999998</v>
       </c>
@@ -11072,11 +11026,11 @@
         <f>SUMPRODUCT(B16:M16,'参数设置'!$E$4:$E$15)</f>
         <v>-0.06571119226883793</v>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="12">
         <f>P15*(1+O16)</f>
         <v>1.0588753384323621</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="Q16" s="12">
         <f>Q15*(1+N16)</f>
         <v>0.9975199999999999</v>
       </c>
@@ -11145,11 +11099,11 @@
         <f>SUMPRODUCT(B17:M17,'参数设置'!$E$4:$E$15)</f>
         <v>0.01990953804549747</v>
       </c>
-      <c r="P17" s="13">
+      <c r="P17" s="12">
         <f>P16*(1+O17)</f>
         <v>1.0799570572683201</v>
       </c>
-      <c r="Q17" s="13">
+      <c r="Q17" s="12">
         <f>Q16*(1+N17)</f>
         <v>1.01196</v>
       </c>
@@ -11218,11 +11172,11 @@
         <f>SUMPRODUCT(B18:M18,'参数设置'!$E$4:$E$15)</f>
         <v>0.043947961278318</v>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="12">
         <f>P17*(1+O18)</f>
         <v>1.1274189682033946</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="Q18" s="12">
         <f>Q17*(1+N18)</f>
         <v>1.0435999999999999</v>
       </c>
@@ -11291,11 +11245,11 @@
         <f>SUMPRODUCT(B19:M19,'参数设置'!$E$4:$E$15)</f>
         <v>0.04226941513310616</v>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="12">
         <f>P18*(1+O19)</f>
         <v>1.1750743085993223</v>
       </c>
-      <c r="Q19" s="13">
+      <c r="Q19" s="12">
         <f>Q18*(1+N19)</f>
         <v>1.0785799999999999</v>
       </c>
@@ -11364,11 +11318,11 @@
         <f>SUMPRODUCT(B20:M20,'参数设置'!$E$4:$E$15)</f>
         <v>0.0276081557207723</v>
       </c>
-      <c r="P20" s="13">
+      <c r="P20" s="12">
         <f>P19*(1+O20)</f>
         <v>1.2075159430946112</v>
       </c>
-      <c r="Q20" s="13">
+      <c r="Q20" s="12">
         <f>Q19*(1+N20)</f>
         <v>1.10202</v>
       </c>
@@ -11437,11 +11391,11 @@
         <f>SUMPRODUCT(B21:M21,'参数设置'!$E$4:$E$15)</f>
         <v>0.05249246842142453</v>
       </c>
-      <c r="P21" s="13">
+      <c r="P21" s="12">
         <f>P20*(1+O21)</f>
         <v>1.2709014356058717</v>
       </c>
-      <c r="Q21" s="13">
+      <c r="Q21" s="12">
         <f>Q20*(1+N21)</f>
         <v>1.1561</v>
       </c>
@@ -11510,11 +11464,11 @@
         <f>SUMPRODUCT(B22:M22,'参数设置'!$E$4:$E$15)</f>
         <v>-0.006462350335248799</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="12">
         <f>P21*(1+O22)</f>
         <v>1.262688425287416</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="12">
         <f>Q21*(1+N22)</f>
         <v>1.14632</v>
       </c>
@@ -11583,11 +11537,11 @@
         <f>SUMPRODUCT(B23:M23,'参数设置'!$E$4:$E$15)</f>
         <v>-0.005440672089627106</v>
       </c>
-      <c r="P23" s="13">
+      <c r="P23" s="12">
         <f>P22*(1+O23)</f>
         <v>1.2558185516140596</v>
       </c>
-      <c r="Q23" s="13">
+      <c r="Q23" s="12">
         <f>Q22*(1+N23)</f>
         <v>1.13662</v>
       </c>
@@ -11656,11 +11610,11 @@
         <f>SUMPRODUCT(B24:M24,'参数设置'!$E$4:$E$15)</f>
         <v>0.007554182370882454</v>
       </c>
-      <c r="P24" s="13">
+      <c r="P24" s="12">
         <f>P23*(1+O24)</f>
         <v>1.2653052339776898</v>
       </c>
-      <c r="Q24" s="13">
+      <c r="Q24" s="12">
         <f>Q23*(1+N24)</f>
         <v>1.14083</v>
       </c>
@@ -11713,17 +11667,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="7" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" customWidth="1"/>
     <col min="8" max="9" width="3.7109375" customWidth="1"/>
-    <col min="10" max="12" width="15.7109375" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11732,34 +11688,23 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-    </row>
     <row r="3" spans="1:13">
       <c r="J3" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:13" ht="26" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
@@ -11771,18 +11716,18 @@
         <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <f>SUM(G5:G16)</f>
         <v>-523000.0</v>
       </c>
@@ -11790,7 +11735,7 @@
         <f>K4/'参数设置'!$B$3</f>
         <v>-0.0523</v>
       </c>
-      <c r="M4" s="4" t="str">
+      <c r="M4" s="14" t="str">
         <f>IF(L4&lt;=-15%,"高风险",IF(L4&lt;0,"中风险","正向情景"))</f>
         <v>中风险</v>
       </c>
@@ -11813,18 +11758,18 @@
         <f>'参数设置'!B22</f>
         <v>-0.08</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <f>D5*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <f>E5*F5</f>
         <v>-80000.0</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <f>SUM(G17:G28)</f>
         <v>-1676000.0</v>
       </c>
@@ -11832,7 +11777,7 @@
         <f>K5/'参数设置'!$B$3</f>
         <v>-0.1676</v>
       </c>
-      <c r="M5" s="4" t="str">
+      <c r="M5" s="14" t="str">
         <f>IF(L5&lt;=-15%,"高风险",IF(L5&lt;0,"中风险","正向情景"))</f>
         <v>高风险</v>
       </c>
@@ -11855,18 +11800,18 @@
         <f>'参数设置'!B22</f>
         <v>-0.08</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f>D6*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f>E6*F6</f>
         <v>-72000.0</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <f>SUM(G29:G40)</f>
         <v>986000.0</v>
       </c>
@@ -11874,7 +11819,7 @@
         <f>K6/'参数设置'!$B$3</f>
         <v>0.0986</v>
       </c>
-      <c r="M6" s="4" t="str">
+      <c r="M6" s="14" t="str">
         <f>IF(L6&lt;=-15%,"高风险",IF(L6&lt;0,"中风险","正向情景"))</f>
         <v>正向情景</v>
       </c>
@@ -11897,11 +11842,11 @@
         <f>'参数设置'!B23</f>
         <v>-0.05</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <f>D7*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <f>E7*F7</f>
         <v>-50000.0</v>
       </c>
@@ -11924,11 +11869,11 @@
         <f>'参数设置'!B23</f>
         <v>-0.05</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <f>D8*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <f>E8*F8</f>
         <v>-40000.0</v>
       </c>
@@ -11951,11 +11896,11 @@
         <f>'参数设置'!B24</f>
         <v>-0.03</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <f>D9*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <f>E9*F9</f>
         <v>-27000.0</v>
       </c>
@@ -11978,11 +11923,11 @@
         <f>'参数设置'!B24</f>
         <v>-0.03</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <f>D10*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <f>E10*F10</f>
         <v>-21000.000000000004</v>
       </c>
@@ -12005,11 +11950,11 @@
         <f>'参数设置'!B25</f>
         <v>-0.04</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <f>D11*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <f>E11*F11</f>
         <v>-36000.0</v>
       </c>
@@ -12032,11 +11977,11 @@
         <f>'参数设置'!B25</f>
         <v>-0.04</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <f>D12*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <f>E12*F12</f>
         <v>-32000.0</v>
       </c>
@@ -12059,11 +12004,11 @@
         <f>'参数设置'!B26</f>
         <v>-0.06</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <f>D13*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <f>E13*F13</f>
         <v>-48000.0</v>
       </c>
@@ -12086,11 +12031,11 @@
         <f>'参数设置'!B26</f>
         <v>-0.06</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <f>D14*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="13">
         <f>E14*F14</f>
         <v>-42000.00000000001</v>
       </c>
@@ -12113,11 +12058,11 @@
         <f>'参数设置'!B27</f>
         <v>-0.05</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <f>D15*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <f>E15*F15</f>
         <v>-40000.0</v>
       </c>
@@ -12140,11 +12085,11 @@
         <f>'参数设置'!B27</f>
         <v>-0.05</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <f>D16*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <f>E16*F16</f>
         <v>-35000.00000000001</v>
       </c>
@@ -12167,11 +12112,11 @@
         <f>'参数设置'!C22</f>
         <v>-0.18</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <f>D17*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="13">
         <f>E17*F17</f>
         <v>-180000.0</v>
       </c>
@@ -12194,11 +12139,11 @@
         <f>'参数设置'!C22</f>
         <v>-0.18</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="13">
         <f>D18*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="13">
         <f>E18*F18</f>
         <v>-162000.0</v>
       </c>
@@ -12221,11 +12166,11 @@
         <f>'参数设置'!C23</f>
         <v>-0.22</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <f>D19*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="13">
         <f>E19*F19</f>
         <v>-220000.0</v>
       </c>
@@ -12248,11 +12193,11 @@
         <f>'参数设置'!C23</f>
         <v>-0.22</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <f>D20*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="13">
         <f>E20*F20</f>
         <v>-176000.0</v>
       </c>
@@ -12275,11 +12220,11 @@
         <f>'参数设置'!C24</f>
         <v>-0.1</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <f>D21*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="13">
         <f>E21*F21</f>
         <v>-90000.0</v>
       </c>
@@ -12302,11 +12247,11 @@
         <f>'参数设置'!C24</f>
         <v>-0.1</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13">
         <f>D22*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="13">
         <f>E22*F22</f>
         <v>-70000.00000000001</v>
       </c>
@@ -12329,11 +12274,11 @@
         <f>'参数设置'!C25</f>
         <v>-0.14</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="13">
         <f>D23*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="13">
         <f>E23*F23</f>
         <v>-126000.00000000001</v>
       </c>
@@ -12356,11 +12301,11 @@
         <f>'参数设置'!C25</f>
         <v>-0.14</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="13">
         <f>D24*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="13">
         <f>E24*F24</f>
         <v>-112000.00000000001</v>
       </c>
@@ -12383,11 +12328,11 @@
         <f>'参数设置'!C26</f>
         <v>-0.17</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="13">
         <f>D25*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="13">
         <f>E25*F25</f>
         <v>-136000.0</v>
       </c>
@@ -12410,11 +12355,11 @@
         <f>'参数设置'!C26</f>
         <v>-0.17</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="13">
         <f>D26*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="13">
         <f>E26*F26</f>
         <v>-119000.00000000003</v>
       </c>
@@ -12437,11 +12382,11 @@
         <f>'参数设置'!C27</f>
         <v>-0.19</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <f>D27*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="13">
         <f>E27*F27</f>
         <v>-152000.0</v>
       </c>
@@ -12464,11 +12409,11 @@
         <f>'参数设置'!C27</f>
         <v>-0.19</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <f>D28*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="13">
         <f>E28*F28</f>
         <v>-133000.00000000003</v>
       </c>
@@ -12491,11 +12436,11 @@
         <f>'参数设置'!D22</f>
         <v>0.16</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="13">
         <f>D29*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="13">
         <f>E29*F29</f>
         <v>160000.0</v>
       </c>
@@ -12518,11 +12463,11 @@
         <f>'参数设置'!D22</f>
         <v>0.16</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="13">
         <f>D30*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="13">
         <f>E30*F30</f>
         <v>144000.0</v>
       </c>
@@ -12545,11 +12490,11 @@
         <f>'参数设置'!D23</f>
         <v>0.07</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="13">
         <f>D31*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="13">
         <f>E31*F31</f>
         <v>70000.0</v>
       </c>
@@ -12572,11 +12517,11 @@
         <f>'参数设置'!D23</f>
         <v>0.07</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="13">
         <f>D32*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="13">
         <f>E32*F32</f>
         <v>56000.00000000001</v>
       </c>
@@ -12599,11 +12544,11 @@
         <f>'参数设置'!D24</f>
         <v>0.09</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="13">
         <f>D33*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="13">
         <f>E33*F33</f>
         <v>81000.0</v>
       </c>
@@ -12626,11 +12571,11 @@
         <f>'参数设置'!D24</f>
         <v>0.09</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="13">
         <f>D34*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="13">
         <f>E34*F34</f>
         <v>63000.00000000001</v>
       </c>
@@ -12653,11 +12598,11 @@
         <f>'参数设置'!D25</f>
         <v>0.11</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="13">
         <f>D35*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="13">
         <f>E35*F35</f>
         <v>99000.0</v>
       </c>
@@ -12680,11 +12625,11 @@
         <f>'参数设置'!D25</f>
         <v>0.11</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="13">
         <f>D36*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="13">
         <f>E36*F36</f>
         <v>88000.0</v>
       </c>
@@ -12707,11 +12652,11 @@
         <f>'参数设置'!D26</f>
         <v>0.05</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="13">
         <f>D37*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="13">
         <f>E37*F37</f>
         <v>40000.0</v>
       </c>
@@ -12734,11 +12679,11 @@
         <f>'参数设置'!D26</f>
         <v>0.05</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="13">
         <f>D38*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="13">
         <f>E38*F38</f>
         <v>35000.00000000001</v>
       </c>
@@ -12761,11 +12706,11 @@
         <f>'参数设置'!D27</f>
         <v>0.1</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="13">
         <f>D39*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="13">
         <f>E39*F39</f>
         <v>80000.0</v>
       </c>
@@ -12788,19 +12733,18 @@
         <f>'参数设置'!D27</f>
         <v>0.1</v>
       </c>
-      <c r="F40" s="14">
+      <c r="F40" s="13">
         <f>D40*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="13">
         <f>E40*F40</f>
         <v>70000.00000000001</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G40">
     <cfRule type="colorScale" priority="1">
@@ -12826,14 +12770,15 @@
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="5" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="3.7109375" customWidth="1"/>
     <col min="7" max="12" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28" customHeight="1">
+    <row r="1" spans="1:12" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12847,64 +12792,64 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:12" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="D3" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="G3" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="15"/>
-      <c r="J3" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="15"/>
+      <c r="E3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <f>'组合分析'!B22</f>
         <v>0.13062683565537636</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="D4" s="16">
+      <c r="B4" s="15"/>
+      <c r="D4" s="15">
         <f>'组合分析'!B23</f>
         <v>0.11455607034702364</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="G4" s="16">
+      <c r="E4" s="15"/>
+      <c r="G4" s="15">
         <f>'组合分析'!B25/'参数设置'!B3</f>
         <v>0.05439930944790144</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="J4" s="16">
+      <c r="H4" s="15"/>
+      <c r="J4" s="15">
         <f>'组合分析'!B27</f>
         <v>-0.1293314203092506</v>
       </c>
-      <c r="K4" s="16"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
@@ -12916,18 +12861,18 @@
         <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="14" t="str">
         <f>'组合分析'!A6</f>
         <v>S001</v>
       </c>
-      <c r="C9" s="5" t="str">
+      <c r="C9" s="16" t="str">
         <f>'组合分析'!B6</f>
         <v>华曜科技</v>
       </c>
@@ -12935,7 +12880,7 @@
         <f>'组合分析'!M6</f>
         <v>0.1</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <f>'组合分析'!P6</f>
         <v>69186.57022522126</v>
       </c>
@@ -12944,11 +12889,11 @@
       <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" s="14" t="str">
         <f>'组合分析'!A10</f>
         <v>S005</v>
       </c>
-      <c r="C10" s="5" t="str">
+      <c r="C10" s="16" t="str">
         <f>'组合分析'!B10</f>
         <v>远岭医药</v>
       </c>
@@ -12956,7 +12901,7 @@
         <f>'组合分析'!M10</f>
         <v>0.09</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <f>'组合分析'!P10</f>
         <v>65111.89330989353</v>
       </c>
@@ -12965,11 +12910,11 @@
       <c r="A11" s="4">
         <v>3</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" s="14" t="str">
         <f>'组合分析'!A8</f>
         <v>S003</v>
       </c>
-      <c r="C11" s="5" t="str">
+      <c r="C11" s="16" t="str">
         <f>'组合分析'!B8</f>
         <v>江海银行</v>
       </c>
@@ -12977,7 +12922,7 @@
         <f>'组合分析'!M8</f>
         <v>0.1</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <f>'组合分析'!P8</f>
         <v>63964.67780913862</v>
       </c>
@@ -12986,11 +12931,11 @@
       <c r="A12" s="4">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" s="14" t="str">
         <f>'组合分析'!A9</f>
         <v>S004</v>
       </c>
-      <c r="C12" s="5" t="str">
+      <c r="C12" s="16" t="str">
         <f>'组合分析'!B9</f>
         <v>安信证券</v>
       </c>
@@ -12998,7 +12943,7 @@
         <f>'组合分析'!M9</f>
         <v>0.08</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <f>'组合分析'!P9</f>
         <v>55817.83048664134</v>
       </c>
@@ -13007,11 +12952,11 @@
       <c r="A13" s="4">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B13" s="14" t="str">
         <f>'组合分析'!A17</f>
         <v>S012</v>
       </c>
-      <c r="C13" s="5" t="str">
+      <c r="C13" s="16" t="str">
         <f>'组合分析'!B17</f>
         <v>锐虎机械</v>
       </c>
@@ -13019,7 +12964,7 @@
         <f>'组合分析'!M17</f>
         <v>0.07</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <f>'组合分析'!P17</f>
         <v>54267.000379465695</v>
       </c>
@@ -13046,14 +12991,14 @@
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="11" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="11" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13066,9 +13011,9 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" ht="26" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
@@ -13089,7 +13034,7 @@
         <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -13876,7 +13821,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B30" s="11">
         <f>SUM('参数设置'!E4:E5)</f>
@@ -13903,9 +13848,9 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" ht="26" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>10</v>
@@ -13926,59 +13871,59 @@
         <v>35</v>
       </c>
       <c r="H32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="12">
         <f>COVARIANCE.S(B$4:B$26,B$4:B$26)</f>
         <v>0.0013524084576669244</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="12">
         <f>COVARIANCE.S(B$4:B$26,C$4:C$26)</f>
         <v>0.001199265661419234</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <f>COVARIANCE.S(B$4:B$26,D$4:D$26)</f>
         <v>0.001255970611206699</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="12">
         <f>COVARIANCE.S(B$4:B$26,E$4:E$26)</f>
         <v>0.000678949334674663</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="12">
         <f>COVARIANCE.S(B$4:B$26,F$4:F$26)</f>
         <v>0.0010365458850546678</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="12">
         <f>COVARIANCE.S(B$4:B$26,G$4:G$26)</f>
         <v>0.0014133312018288144</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="12">
         <f>SUMPRODUCT(B33:G33,$B$30:$G$30)</f>
         <v>0.0011566836737324647</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="13">
         <f>B$30*H33*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>109321.76240762952</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="13">
         <f>I33/B$30</f>
         <v>575377.6968822606</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="13">
         <f>B$30*STDEV.S(B$4:B$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>114940.59534792692</v>
       </c>
@@ -13987,43 +13932,43 @@
       <c r="A34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="12">
         <f>COVARIANCE.S(C$4:C$26,B$4:B$26)</f>
         <v>0.001199265661419234</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="12">
         <f>COVARIANCE.S(C$4:C$26,C$4:C$26)</f>
         <v>0.0014632106602867462</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="12">
         <f>COVARIANCE.S(C$4:C$26,D$4:D$26)</f>
         <v>0.0013546728920645023</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="12">
         <f>COVARIANCE.S(C$4:C$26,E$4:E$26)</f>
         <v>0.0007207445205151251</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="12">
         <f>COVARIANCE.S(C$4:C$26,F$4:F$26)</f>
         <v>0.0010089856281822042</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="12">
         <f>COVARIANCE.S(C$4:C$26,G$4:G$26)</f>
         <v>0.0011780811272671613</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="12">
         <f>SUMPRODUCT(B34:G34,$B$30:$G$30)</f>
         <v>0.0011585726390565653</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="13">
         <f>C$30*H34*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>103737.12099213374</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="13">
         <f>I34/C$30</f>
         <v>576317.3388451874</v>
       </c>
-      <c r="K34" s="14">
+      <c r="K34" s="13">
         <f>C$30*STDEV.S(C$4:C$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>113263.98452945186</v>
       </c>
@@ -14032,43 +13977,43 @@
       <c r="A35" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="12">
         <f>COVARIANCE.S(D$4:D$26,B$4:B$26)</f>
         <v>0.001255970611206699</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="12">
         <f>COVARIANCE.S(D$4:D$26,C$4:C$26)</f>
         <v>0.0013546728920645023</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <f>COVARIANCE.S(D$4:D$26,D$4:D$26)</f>
         <v>0.001673939806505305</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="12">
         <f>COVARIANCE.S(D$4:D$26,E$4:E$26)</f>
         <v>0.0008418844015922254</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="12">
         <f>COVARIANCE.S(D$4:D$26,F$4:F$26)</f>
         <v>0.0009422475139068253</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="12">
         <f>COVARIANCE.S(D$4:D$26,G$4:G$26)</f>
         <v>0.0014225041019277726</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="12">
         <f>SUMPRODUCT(B35:G35,$B$30:$G$30)</f>
         <v>0.0012481389963876</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="13">
         <f>D$30*H35*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>99339.35888460213</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="13">
         <f>I35/D$30</f>
         <v>620870.9930287633</v>
       </c>
-      <c r="K35" s="14">
+      <c r="K35" s="13">
         <f>D$30*STDEV.S(D$4:D$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>107685.14656228223</v>
       </c>
@@ -14077,43 +14022,43 @@
       <c r="A36" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="12">
         <f>COVARIANCE.S(E$4:E$26,B$4:B$26)</f>
         <v>0.000678949334674663</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="12">
         <f>COVARIANCE.S(E$4:E$26,C$4:C$26)</f>
         <v>0.0007207445205151251</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <f>COVARIANCE.S(E$4:E$26,D$4:D$26)</f>
         <v>0.0008418844015922254</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="12">
         <f>COVARIANCE.S(E$4:E$26,E$4:E$26)</f>
         <v>0.000528122670100409</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="12">
         <f>COVARIANCE.S(E$4:E$26,F$4:F$26)</f>
         <v>0.0006903472911133862</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="12">
         <f>COVARIANCE.S(E$4:E$26,G$4:G$26)</f>
         <v>0.0008074802628427954</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="12">
         <f>SUMPRODUCT(B36:G36,$B$30:$G$30)</f>
         <v>0.0007078908785461614</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="13">
         <f>E$30*H36*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>59862.33534764133</v>
       </c>
-      <c r="J36" s="14">
+      <c r="J36" s="13">
         <f>I36/E$30</f>
         <v>352131.38439789024</v>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="13">
         <f>E$30*STDEV.S(E$4:E$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>64266.14193147077</v>
       </c>
@@ -14122,43 +14067,43 @@
       <c r="A37" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="12">
         <f>COVARIANCE.S(F$4:F$26,B$4:B$26)</f>
         <v>0.0010365458850546678</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="12">
         <f>COVARIANCE.S(F$4:F$26,C$4:C$26)</f>
         <v>0.0010089856281822042</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <f>COVARIANCE.S(F$4:F$26,D$4:D$26)</f>
         <v>0.0009422475139068253</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="12">
         <f>COVARIANCE.S(F$4:F$26,E$4:E$26)</f>
         <v>0.0006903472911133862</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="12">
         <f>COVARIANCE.S(F$4:F$26,F$4:F$26)</f>
         <v>0.0011838956809813053</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="12">
         <f>COVARIANCE.S(F$4:F$26,G$4:G$26)</f>
         <v>0.0012238657330600076</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="12">
         <f>SUMPRODUCT(B37:G37,$B$30:$G$30)</f>
         <v>0.0010078439850537482</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="13">
         <f>F$30*H37*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>75200.89080175663</v>
       </c>
-      <c r="J37" s="14">
+      <c r="J37" s="13">
         <f>I37/F$30</f>
         <v>501339.2720117108</v>
       </c>
-      <c r="K37" s="14">
+      <c r="K37" s="13">
         <f>F$30*STDEV.S(F$4:F$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>84901.20993122969</v>
       </c>
@@ -14167,88 +14112,88 @@
       <c r="A38" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="12">
         <f>COVARIANCE.S(G$4:G$26,B$4:B$26)</f>
         <v>0.0014133312018288144</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="12">
         <f>COVARIANCE.S(G$4:G$26,C$4:C$26)</f>
         <v>0.0011780811272671613</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <f>COVARIANCE.S(G$4:G$26,D$4:D$26)</f>
         <v>0.0014225041019277726</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="12">
         <f>COVARIANCE.S(G$4:G$26,E$4:E$26)</f>
         <v>0.0008074802628427954</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="12">
         <f>COVARIANCE.S(G$4:G$26,F$4:F$26)</f>
         <v>0.0012238657330600076</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="12">
         <f>COVARIANCE.S(G$4:G$26,G$4:G$26)</f>
         <v>0.0017645284907911445</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="12">
         <f>SUMPRODUCT(B38:G38,$B$30:$G$30)</f>
         <v>0.0012937189658249555</v>
       </c>
-      <c r="I38" s="14">
+      <c r="I38" s="13">
         <f>G$30*H38*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>96531.62604525105</v>
       </c>
-      <c r="J38" s="14">
+      <c r="J38" s="13">
         <f>I38/G$30</f>
         <v>643544.1736350069</v>
       </c>
-      <c r="K38" s="14">
+      <c r="K38" s="13">
         <f>G$30*STDEV.S(G$4:G$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>103650.52325439315</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B41" s="13">
+        <v>111</v>
+      </c>
+      <c r="B41" s="12">
         <f>B30*H33+C30*H34+D30*H35+E30*H36+F30*H37+G30*H38</f>
         <v>0.001093591104446019</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" s="14">
+        <v>112</v>
+      </c>
+      <c r="B42" s="13">
         <f>SQRT(B41)*'参数设置'!B3*'参数设置'!B7</f>
         <v>543993.0944790144</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="14">
+        <v>113</v>
+      </c>
+      <c r="B43" s="13">
         <f>SUM(I33:I38)</f>
         <v>543993.0944790144</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B44" s="14">
+        <v>114</v>
+      </c>
+      <c r="B44" s="13">
         <f>SUM(K33:K38)-B42</f>
         <v>44714.50707774027</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B45" s="5" t="str">
+        <v>115</v>
+      </c>
+      <c r="B45" s="16" t="str">
         <f>INDEX(A33:A38,MATCH(MAX(I33:I38),I33:I38,0))</f>
         <v>科技</v>
       </c>
@@ -14276,14 +14221,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="10" width="18.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="13" width="3.7109375" customWidth="1"/>
-    <col min="14" max="15" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14295,42 +14247,42 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="36" customHeight="1">
+    <row r="3" spans="1:15" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -14345,7 +14297,7 @@
         <f>STDEV.S('月度收益'!O2:O13)*SQRT(12)</f>
         <v>0.10483841241923837</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <f>SLOPE('月度收益'!O2:O13,'月度收益'!N2:N13)</f>
         <v>1.015946486762296</v>
       </c>
@@ -14361,11 +14313,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O2:O13,1),SMALL('月度收益'!O2:O13,2)))</f>
         <v>0.02610491021506569</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f>IF(B4&lt;-F4,1,0)</f>
         <v>1</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <f>AVERAGE($O$4:$O$15)*12/E4</f>
         <v>9.264631633450582</v>
       </c>
@@ -14393,7 +14345,7 @@
         <f>STDEV.S('月度收益'!O3:O14)*SQRT(12)</f>
         <v>0.11065526195536365</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>SLOPE('月度收益'!O3:O14,'月度收益'!N3:N14)</f>
         <v>1.0160922076307974</v>
       </c>
@@ -14409,11 +14361,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O3:O14,1),SMALL('月度收益'!O3:O14,2)))</f>
         <v>0.03396154818892115</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>IF(B5&lt;-F5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>AVERAGE($O$5:$O$16)*12/E5</f>
         <v>9.042857600384956</v>
       </c>
@@ -14441,7 +14393,7 @@
         <f>STDEV.S('月度收益'!O4:O15)*SQRT(12)</f>
         <v>0.11422690277540343</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>SLOPE('月度收益'!O4:O15,'月度收益'!N4:N15)</f>
         <v>1.0285783366770354</v>
       </c>
@@ -14457,11 +14409,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O4:O15,1),SMALL('月度收益'!O4:O15,2)))</f>
         <v>0.03396154818892115</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>IF(B6&lt;-F6,1,0)</f>
         <v>1</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>AVERAGE($O$6:$O$17)*12/E6</f>
         <v>6.202833536449956</v>
       </c>
@@ -14489,7 +14441,7 @@
         <f>STDEV.S('月度收益'!O5:O16)*SQRT(12)</f>
         <v>0.1336380507168803</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f>SLOPE('月度收益'!O5:O16,'月度收益'!N5:N16)</f>
         <v>1.04673088324702</v>
       </c>
@@ -14505,11 +14457,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O5:O16,1),SMALL('月度收益'!O5:O16,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <f>IF(B7&lt;-F7,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f>AVERAGE($O$7:$O$18)*12/E7</f>
         <v>4.707270425713751</v>
       </c>
@@ -14537,7 +14489,7 @@
         <f>STDEV.S('月度收益'!O6:O17)*SQRT(12)</f>
         <v>0.13532638138870484</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>SLOPE('月度收益'!O6:O17,'月度收益'!N6:N17)</f>
         <v>1.0476691231338255</v>
       </c>
@@ -14553,11 +14505,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O6:O17,1),SMALL('月度收益'!O6:O17,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f>IF(B8&lt;-F8,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>AVERAGE($O$8:$O$19)*12/E8</f>
         <v>5.217404301783672</v>
       </c>
@@ -14585,7 +14537,7 @@
         <f>STDEV.S('月度收益'!O7:O18)*SQRT(12)</f>
         <v>0.1420188468336544</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>SLOPE('月度收益'!O7:O18,'月度收益'!N7:N18)</f>
         <v>1.0630018986628158</v>
       </c>
@@ -14601,11 +14553,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O7:O18,1),SMALL('月度收益'!O7:O18,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <f>IF(B9&lt;-F9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>AVERAGE($O$9:$O$20)*12/E9</f>
         <v>4.402378630799633</v>
       </c>
@@ -14633,7 +14585,7 @@
         <f>STDEV.S('月度收益'!O8:O19)*SQRT(12)</f>
         <v>0.14685936596862115</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f>SLOPE('月度收益'!O8:O19,'月度收益'!N8:N19)</f>
         <v>1.0666734740893153</v>
       </c>
@@ -14649,11 +14601,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O8:O19,1),SMALL('月度收益'!O8:O19,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <f>IF(B10&lt;-F10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f>AVERAGE($O$10:$O$21)*12/E10</f>
         <v>4.492276654027392</v>
       </c>
@@ -14681,7 +14633,7 @@
         <f>STDEV.S('月度收益'!O9:O20)*SQRT(12)</f>
         <v>0.13844296359137812</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>SLOPE('月度收益'!O9:O20,'月度收益'!N9:N20)</f>
         <v>1.0720413057505451</v>
       </c>
@@ -14697,11 +14649,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O9:O20,1),SMALL('月度收益'!O9:O20,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <f>IF(B11&lt;-F11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f>AVERAGE($O$11:$O$22)*12/E11</f>
         <v>4.686399089334704</v>
       </c>
@@ -14729,7 +14681,7 @@
         <f>STDEV.S('月度收益'!O10:O21)*SQRT(12)</f>
         <v>0.14251929528228524</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f>SLOPE('月度收益'!O10:O21,'月度收益'!N10:N21)</f>
         <v>1.0615046649827529</v>
       </c>
@@ -14745,11 +14697,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O10:O21,1),SMALL('月度收益'!O10:O21,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <f>IF(B12&lt;-F12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f>AVERAGE($O$12:$O$23)*12/E12</f>
         <v>4.462415202672049</v>
       </c>
@@ -14777,7 +14729,7 @@
         <f>STDEV.S('月度收益'!O11:O22)*SQRT(12)</f>
         <v>0.14121341961734585</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>SLOPE('月度收益'!O11:O22,'月度收益'!N11:N22)</f>
         <v>1.0661535884572453</v>
       </c>
@@ -14793,11 +14745,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O11:O22,1),SMALL('月度收益'!O11:O22,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f>IF(B13&lt;-F13,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>AVERAGE($O$13:$O$24)*12/E13</f>
         <v>4.151412468168613</v>
       </c>
@@ -14825,7 +14777,7 @@
         <f>STDEV.S('月度收益'!O12:O23)*SQRT(12)</f>
         <v>0.1223065066275717</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f>SLOPE('月度收益'!O12:O23,'月度收益'!N12:N23)</f>
         <v>1.0870556443068415</v>
       </c>
@@ -14841,11 +14793,11 @@
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O12:O23,1),SMALL('月度收益'!O12:O23,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="12">
         <f>IF(B14&lt;-F14,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <f>AVERAGE($O$14:$O$25)*12/E14</f>
         <v>3.942987023247805</v>
       </c>
@@ -14881,9 +14833,9 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="13">
+        <v>128</v>
+      </c>
+      <c r="B17" s="12">
         <f>SUM(H4:H14)</f>
         <v>2</v>
       </c>
@@ -14897,7 +14849,7 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B18" s="11">
         <f>B17/COUNT(B4:B14)</f>
@@ -14913,9 +14865,9 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="13">
+        <v>130</v>
+      </c>
+      <c r="B19" s="12">
         <f>COUNT(B4:B14)*10%</f>
         <v>1.1</v>
       </c>
@@ -14929,9 +14881,9 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B20" s="5" t="str">
+        <v>131</v>
+      </c>
+      <c r="B20" s="16" t="str">
         <f>IF(B17&lt;=2,"正常","复核")</f>
         <v>正常</v>
       </c>

--- a/股票组合风险分析_参考答案.xlsx
+++ b/股票组合风险分析_参考答案.xlsx
@@ -432,7 +432,7 @@
     <numFmt numFmtId="166" formatCode="¥#,##0;[Red]-¥#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,66 +442,19 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -531,10 +484,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -547,23 +500,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8749,7 +8693,7 @@
       <c r="D16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <f>SUM(E4:E15)</f>
         <v>1.0</v>
       </c>
@@ -8977,59 +8921,59 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="6">
         <f>'原始行情'!E279</f>
         <v>20.5</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="6">
         <f>'原始行情'!E3</f>
         <v>18.0</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>PRODUCT(1+'月度收益'!B$2:B$24)-1</f>
         <v>0.1488490680035477</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f>(1+F6)^(12/23)-1</f>
         <v>0.07508190658720038</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <f>STDEV.S('月度收益'!B$2:B$24)*SQRT(12)</f>
         <v>0.1456956289744867</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="6">
         <f>SLOPE('月度收益'!B$2:B$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.2767811493183567</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <f>'参数设置'!$B$4+I6*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.08476672921364378</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <f>G6-J6</f>
         <v>-0.009684822626443407</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!B$2:B$24&lt;0)*'月度收益'!B$2:B$24*'月度收益'!B$2:B$24)/COUNTIF('月度收益'!B$2:B$24,"&lt;0"))*SQRT(12)</f>
         <v>0.12326337609280806</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <f>'参数设置'!E4</f>
         <v>0.1</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <f>M6*G6</f>
         <v>0.007508190658720038</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="6">
         <f>M6*I6</f>
         <v>0.12767811493183567</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="9">
         <f>M6*'参数设置'!$B$3*'参数设置'!$B$7*H6/SQRT(12)</f>
         <v>69186.57022522126</v>
       </c>
-      <c r="Q6" s="14" t="str">
+      <c r="Q6" s="4" t="str">
         <f>IF(AND(K6&gt;1.5%,I6&lt;1.15),"增配观察",IF(K6&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9044,59 +8988,59 @@
       <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="6">
         <f>'原始行情'!E280</f>
         <v>25.96</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="6">
         <f>'原始行情'!E4</f>
         <v>21.15</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f>PRODUCT(1+'月度收益'!C$2:C$24)-1</f>
         <v>0.23776348164741434</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f>(1+F7)^(12/23)-1</f>
         <v>0.1177191581110264</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <f>STDEV.S('月度收益'!C$2:C$24)*SQRT(12)</f>
         <v>0.12055472227851159</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="6">
         <f>SLOPE('月度收益'!C$2:C$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.9053807458088171</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <f>'参数设置'!$B$4+I7*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.06650863653318181</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <f>G7-J7</f>
         <v>0.05121052157784459</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!C$2:C$24&lt;0)*'月度收益'!C$2:C$24*'月度收益'!C$2:C$24)/COUNTIF('月度收益'!C$2:C$24,"&lt;0"))*SQRT(12)</f>
         <v>0.1391463706132178</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <f>'参数设置'!E5</f>
         <v>0.09</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <f>M7*G7</f>
         <v>0.010594724229992376</v>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="6">
         <f>M7*I7</f>
         <v>0.08148426712279354</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="9">
         <f>M7*'参数设置'!$B$3*'参数设置'!$B$7*H7/SQRT(12)</f>
         <v>51523.103581428535</v>
       </c>
-      <c r="Q7" s="14" t="str">
+      <c r="Q7" s="4" t="str">
         <f>IF(AND(K7&gt;1.5%,I7&lt;1.15),"增配观察",IF(K7&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9111,59 +9055,59 @@
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="6">
         <f>'原始行情'!E281</f>
         <v>30.48</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="6">
         <f>'原始行情'!E5</f>
         <v>24.3</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>PRODUCT(1+'月度收益'!D$2:D$24)-1</f>
         <v>0.2642337861316264</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <f>(1+F8)^(12/23)-1</f>
         <v>0.1301272195835621</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <f>STDEV.S('月度收益'!D$2:D$24)*SQRT(12)</f>
         <v>0.13469917550784388</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="6">
         <f>SLOPE('月度收益'!D$2:D$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.0547850693234158</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <f>'参数设置'!$B$4+I8*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.07385337272575086</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="10">
         <f>G8-J8</f>
         <v>0.05627384685781124</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!D$2:D$24&lt;0)*'月度收益'!D$2:D$24*'月度收益'!D$2:D$24)/COUNTIF('月度收益'!D$2:D$24,"&lt;0"))*SQRT(12)</f>
         <v>0.12461113132075254</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="10">
         <f>'参数设置'!E6</f>
         <v>0.1</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="10">
         <f>M8*G8</f>
         <v>0.013012721958356212</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="6">
         <f>M8*I8</f>
         <v>0.10547850693234158</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="9">
         <f>M8*'参数设置'!$B$3*'参数设置'!$B$7*H8/SQRT(12)</f>
         <v>63964.67780913862</v>
       </c>
-      <c r="Q8" s="14" t="str">
+      <c r="Q8" s="4" t="str">
         <f>IF(AND(K8&gt;1.5%,I8&lt;1.15),"增配观察",IF(K8&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9178,59 +9122,59 @@
       <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="6">
         <f>'原始行情'!E282</f>
         <v>35.75</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="6">
         <f>'原始行情'!E6</f>
         <v>27.45</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f>PRODUCT(1+'月度收益'!E$2:E$24)-1</f>
         <v>0.3122932456601526</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <f>(1+F9)^(12/23)-1</f>
         <v>0.1523418530794396</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <f>STDEV.S('月度收益'!E$2:E$24)*SQRT(12)</f>
         <v>0.14692905527527328</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="6">
         <f>SLOPE('月度收益'!E$2:E$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.1958995667562984</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <f>'参数设置'!$B$4+I9*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.08079057997792394</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="10">
         <f>G9-J9</f>
         <v>0.07155127310151566</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!E$2:E$24&lt;0)*'月度收益'!E$2:E$24*'月度收益'!E$2:E$24)/COUNTIF('月度收益'!E$2:E$24,"&lt;0"))*SQRT(12)</f>
         <v>0.12604139327636044</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="10">
         <f>'参数设置'!E7</f>
         <v>0.08</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="10">
         <f>M9*G9</f>
         <v>0.012187348246355168</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="6">
         <f>M9*I9</f>
         <v>0.09567196534050387</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="9">
         <f>M9*'参数设置'!$B$3*'参数设置'!$B$7*H9/SQRT(12)</f>
         <v>55817.83048664134</v>
       </c>
-      <c r="Q9" s="14" t="str">
+      <c r="Q9" s="4" t="str">
         <f>IF(AND(K9&gt;1.5%,I9&lt;1.15),"增配观察",IF(K9&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9245,59 +9189,59 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="6">
         <f>'原始行情'!E283</f>
         <v>37.66</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="6">
         <f>'原始行情'!E7</f>
         <v>30.6</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f>PRODUCT(1+'月度收益'!F$2:F$24)-1</f>
         <v>0.24003147534949654</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <f>(1+F10)^(12/23)-1</f>
         <v>0.11878722910434703</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f>STDEV.S('月度收益'!F$2:F$24)*SQRT(12)</f>
         <v>0.15235002686894922</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="6">
         <f>SLOPE('月度收益'!F$2:F$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.2477179581923739</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <f>'参数设置'!$B$4+I10*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.08333797891570678</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="10">
         <f>G10-J10</f>
         <v>0.035449250188640244</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!F$2:F$24&lt;0)*'月度收益'!F$2:F$24*'月度收益'!F$2:F$24)/COUNTIF('月度收益'!F$2:F$24,"&lt;0"))*SQRT(12)</f>
         <v>0.15505311981828174</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="10">
         <f>'参数设置'!E8</f>
         <v>0.09</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="10">
         <f>M10*G10</f>
         <v>0.010690850619391231</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="6">
         <f>M10*I10</f>
         <v>0.11229461623731364</v>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="9">
         <f>M10*'参数设置'!$B$3*'参数设置'!$B$7*H10/SQRT(12)</f>
         <v>65111.89330989353</v>
       </c>
-      <c r="Q10" s="14" t="str">
+      <c r="Q10" s="4" t="str">
         <f>IF(AND(K10&gt;1.5%,I10&lt;1.15),"增配观察",IF(K10&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9312,59 +9256,59 @@
       <c r="C11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="6">
         <f>'原始行情'!E284</f>
         <v>42.79</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="6">
         <f>'原始行情'!E8</f>
         <v>33.75</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f>PRODUCT(1+'月度收益'!G$2:G$24)-1</f>
         <v>0.2770151907933558</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <f>(1+F11)^(12/23)-1</f>
         <v>0.13607405504986003</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <f>STDEV.S('月度收益'!G$2:G$24)*SQRT(12)</f>
         <v>0.14193508207629768</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="6">
         <f>SLOPE('月度收益'!G$2:G$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.146751788731645</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <f>'参数设置'!$B$4+I11*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.07837446874666662</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="10">
         <f>G11-J11</f>
         <v>0.05769958630319341</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!G$2:G$24&lt;0)*'月度收益'!G$2:G$24*'月度收益'!G$2:G$24)/COUNTIF('月度收益'!G$2:G$24,"&lt;0"))*SQRT(12)</f>
         <v>0.12260052075072218</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="10">
         <f>'参数设置'!E9</f>
         <v>0.07</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="10">
         <f>M11*G11</f>
         <v>0.009525183853490203</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="6">
         <f>M11*I11</f>
         <v>0.08027262521121516</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="9">
         <f>M11*'参数设置'!$B$3*'参数设置'!$B$7*H11/SQRT(12)</f>
         <v>47180.55795379937</v>
       </c>
-      <c r="Q11" s="14" t="str">
+      <c r="Q11" s="4" t="str">
         <f>IF(AND(K11&gt;1.5%,I11&lt;1.15),"增配观察",IF(K11&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9379,59 +9323,59 @@
       <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="6">
         <f>'原始行情'!E285</f>
         <v>45.63</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="6">
         <f>'原始行情'!E9</f>
         <v>36.9</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f>PRODUCT(1+'月度收益'!H$2:H$24)-1</f>
         <v>0.24561171442789176</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f>(1+F12)^(12/23)-1</f>
         <v>0.12141117238882648</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <f>STDEV.S('月度收益'!H$2:H$24)*SQRT(12)</f>
         <v>0.10340249541263921</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="6">
         <f>SLOPE('月度收益'!H$2:H$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.7096873510466656</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f>'参数设置'!$B$4+I12*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.056888323510474445</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <f>G12-J12</f>
         <v>0.06452284887835204</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!H$2:H$24&lt;0)*'月度收益'!H$2:H$24*'月度收益'!H$2:H$24)/COUNTIF('月度收益'!H$2:H$24,"&lt;0"))*SQRT(12)</f>
         <v>0.10764621967712795</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <f>'参数设置'!E10</f>
         <v>0.09</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="10">
         <f>M12*G12</f>
         <v>0.010927005514994382</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="6">
         <f>M12*I12</f>
         <v>0.0638718615941999</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="9">
         <f>M12*'参数设置'!$B$3*'参数设置'!$B$7*H12/SQRT(12)</f>
         <v>44192.5242000514</v>
       </c>
-      <c r="Q12" s="14" t="str">
+      <c r="Q12" s="4" t="str">
         <f>IF(AND(K12&gt;1.5%,I12&lt;1.15),"增配观察",IF(K12&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9446,59 +9390,59 @@
       <c r="C13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="6">
         <f>'原始行情'!E286</f>
         <v>50.69</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="6">
         <f>'原始行情'!E10</f>
         <v>40.05</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f>PRODUCT(1+'月度收益'!I$2:I$24)-1</f>
         <v>0.2746041837662183</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <f>(1+F13)^(12/23)-1</f>
         <v>0.13495446590885574</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <f>STDEV.S('月度收益'!I$2:I$24)*SQRT(12)</f>
         <v>0.09893832677334906</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="6">
         <f>SLOPE('月度收益'!I$2:I$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.6635655624507926</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <f>'参数设置'!$B$4+I13*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.05462097031749254</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <f>G13-J13</f>
         <v>0.0803334955913632</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!I$2:I$24&lt;0)*'月度收益'!I$2:I$24*'月度收益'!I$2:I$24)/COUNTIF('月度收益'!I$2:I$24,"&lt;0"))*SQRT(12)</f>
         <v>0.07033018954077394</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <f>'参数设置'!E11</f>
         <v>0.08</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="10">
         <f>M13*G13</f>
         <v>0.01079635727270846</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="6">
         <f>M13*I13</f>
         <v>0.05308524499606341</v>
       </c>
-      <c r="P13" s="13">
+      <c r="P13" s="9">
         <f>M13*'参数设置'!$B$3*'参数设置'!$B$7*H13/SQRT(12)</f>
         <v>37586.32179401287</v>
       </c>
-      <c r="Q13" s="14" t="str">
+      <c r="Q13" s="4" t="str">
         <f>IF(AND(K13&gt;1.5%,I13&lt;1.15),"增配观察",IF(K13&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9513,59 +9457,59 @@
       <c r="C14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="6">
         <f>'原始行情'!E287</f>
         <v>52.34</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="6">
         <f>'原始行情'!E11</f>
         <v>43.2</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f>PRODUCT(1+'月度收益'!J$2:J$24)-1</f>
         <v>0.2206084761072511</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <f>(1+F14)^(12/23)-1</f>
         <v>0.10960980569378531</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <f>STDEV.S('月度收益'!J$2:J$24)*SQRT(12)</f>
         <v>0.12796348354711454</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="6">
         <f>SLOPE('月度收益'!J$2:J$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.9891348209809542</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <f>'参数设置'!$B$4+I14*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.07062599788338286</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <f>G14-J14</f>
         <v>0.03898380781040245</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!J$2:J$24&lt;0)*'月度收益'!J$2:J$24*'月度收益'!J$2:J$24)/COUNTIF('月度收益'!J$2:J$24,"&lt;0"))*SQRT(12)</f>
         <v>0.11711826143503869</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="10">
         <f>'参数设置'!E12</f>
         <v>0.08</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="10">
         <f>M14*G14</f>
         <v>0.008768784455502825</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="6">
         <f>M14*I14</f>
         <v>0.07913078567847634</v>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="9">
         <f>M14*'参数设置'!$B$3*'参数设置'!$B$7*H14/SQRT(12)</f>
         <v>48612.87660041869</v>
       </c>
-      <c r="Q14" s="14" t="str">
+      <c r="Q14" s="4" t="str">
         <f>IF(AND(K14&gt;1.5%,I14&lt;1.15),"增配观察",IF(K14&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9580,59 +9524,59 @@
       <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="6">
         <f>'原始行情'!E288</f>
         <v>57.74</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="6">
         <f>'原始行情'!E12</f>
         <v>46.35</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f>PRODUCT(1+'月度收益'!K$2:K$24)-1</f>
         <v>0.2549891016903554</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <f>(1+F15)^(12/23)-1</f>
         <v>0.12580798344363342</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <f>STDEV.S('月度收益'!K$2:K$24)*SQRT(12)</f>
         <v>0.12549312207531008</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="6">
         <f>SLOPE('月度收益'!K$2:K$24,'月度收益'!$N$2:$N$24)</f>
         <v>0.9834282584451242</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <f>'参数设置'!$B$4+I15*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.07034546251863505</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="10">
         <f>G15-J15</f>
         <v>0.05546252092499837</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!K$2:K$24&lt;0)*'月度收益'!K$2:K$24*'月度收益'!K$2:K$24)/COUNTIF('月度收益'!K$2:K$24,"&lt;0"))*SQRT(12)</f>
         <v>0.10227087655939598</v>
       </c>
-      <c r="M15" s="11">
+      <c r="M15" s="10">
         <f>'参数设置'!E13</f>
         <v>0.07</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="10">
         <f>M15*G15</f>
         <v>0.00880655884105434</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="6">
         <f>M15*I15</f>
         <v>0.0688399780911587</v>
       </c>
-      <c r="P15" s="13">
+      <c r="P15" s="9">
         <f>M15*'参数设置'!$B$3*'参数设置'!$B$7*H15/SQRT(12)</f>
         <v>41715.095607544165</v>
       </c>
-      <c r="Q15" s="14" t="str">
+      <c r="Q15" s="4" t="str">
         <f>IF(AND(K15&gt;1.5%,I15&lt;1.15),"增配观察",IF(K15&gt;-1%,"维持","降低暴露"))</f>
         <v>增配观察</v>
       </c>
@@ -9647,59 +9591,59 @@
       <c r="C16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="6">
         <f>'原始行情'!E289</f>
         <v>65.33</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="6">
         <f>'原始行情'!E13</f>
         <v>49.5</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f>PRODUCT(1+'月度收益'!L$2:L$24)-1</f>
         <v>0.32951072410107507</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <f>(1+F16)^(12/23)-1</f>
         <v>0.1602053814271951</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="10">
         <f>STDEV.S('月度收益'!L$2:L$24)*SQRT(12)</f>
         <v>0.14278900532998365</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="6">
         <f>SLOPE('月度收益'!L$2:L$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.1553402857334645</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <f>'参数设置'!$B$4+I16*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.07879668038877397</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <f>G16-J16</f>
         <v>0.08140870103842113</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!L$2:L$24&lt;0)*'月度收益'!L$2:L$24*'月度收益'!L$2:L$24)/COUNTIF('月度收益'!L$2:L$24,"&lt;0"))*SQRT(12)</f>
         <v>0.13919227281716867</v>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="10">
         <f>'参数设置'!E14</f>
         <v>0.08</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="10">
         <f>M16*G16</f>
         <v>0.012816430514175609</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="6">
         <f>M16*I16</f>
         <v>0.09242722285867716</v>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="9">
         <f>M16*'参数设置'!$B$3*'参数设置'!$B$7*H16/SQRT(12)</f>
         <v>54245.04009729691</v>
       </c>
-      <c r="Q16" s="14" t="str">
+      <c r="Q16" s="4" t="str">
         <f>IF(AND(K16&gt;1.5%,I16&lt;1.15),"增配观察",IF(K16&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9714,59 +9658,59 @@
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="6">
         <f>'原始行情'!E290</f>
         <v>71.78</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="6">
         <f>'原始行情'!E14</f>
         <v>52.65</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f>PRODUCT(1+'月度收益'!M$2:M$24)-1</f>
         <v>0.37347850404935756</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <f>(1+F17)^(12/23)-1</f>
         <v>0.18006807392056023</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <f>STDEV.S('月度收益'!M$2:M$24)*SQRT(12)</f>
         <v>0.1632534986219611</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="6">
         <f>SLOPE('月度收益'!M$2:M$24,'月度收益'!$N$2:$N$24)</f>
         <v>1.3806784934734606</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <f>'参数设置'!$B$4+I17*('组合分析'!$B$28-'参数设置'!$B$4)</f>
         <v>0.08987433631614661</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <f>G17-J17</f>
         <v>0.09019373760441363</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="10">
         <f>SQRT(SUMPRODUCT(('月度收益'!M$2:M$24&lt;0)*'月度收益'!M$2:M$24*'月度收益'!M$2:M$24)/COUNTIF('月度收益'!M$2:M$24,"&lt;0"))*SQRT(12)</f>
         <v>0.13042851338464057</v>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="10">
         <f>'参数设置'!E15</f>
         <v>0.07</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="10">
         <f>M17*G17</f>
         <v>0.012604765174439217</v>
       </c>
-      <c r="O17" s="12">
+      <c r="O17" s="6">
         <f>M17*I17</f>
         <v>0.09664749454314225</v>
       </c>
-      <c r="P17" s="13">
+      <c r="P17" s="9">
         <f>M17*'参数设置'!$B$3*'参数设置'!$B$7*H17/SQRT(12)</f>
         <v>54267.000379465695</v>
       </c>
-      <c r="Q17" s="14" t="str">
+      <c r="Q17" s="4" t="str">
         <f>IF(AND(K17&gt;1.5%,I17&lt;1.15),"增配观察",IF(K17&gt;-1%,"维持","降低暴露"))</f>
         <v>维持</v>
       </c>
@@ -9780,7 +9724,7 @@
       <c r="A21" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <f>SUM(M6:M17)</f>
         <v>1.0</v>
       </c>
@@ -9789,7 +9733,7 @@
       <c r="A22" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <f>'月度收益'!P24^(12/23)-1</f>
         <v>0.13062683565537636</v>
       </c>
@@ -9798,7 +9742,7 @@
       <c r="A23" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <f>STDEV.S('月度收益'!O2:O24)*SQRT(12)</f>
         <v>0.11455607034702364</v>
       </c>
@@ -9807,7 +9751,7 @@
       <c r="A24" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="6">
         <f>SUM(O6:O17)</f>
         <v>1.0568826835377212</v>
       </c>
@@ -9816,7 +9760,7 @@
       <c r="A25" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="9">
         <f>'参数设置'!B3*'参数设置'!B7*STDEV.S('月度收益'!O2:O24)</f>
         <v>543993.0944790144</v>
       </c>
@@ -9825,7 +9769,7 @@
       <c r="A26" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="6">
         <f>(B22-'参数设置'!B4)/B23</f>
         <v>0.9482416368361284</v>
       </c>
@@ -9834,7 +9778,7 @@
       <c r="A27" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <f>MIN('月度收益'!R2:R24)</f>
         <v>-0.1293314203092506</v>
       </c>
@@ -9843,7 +9787,7 @@
       <c r="A28" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <f>('原始行情'!G279/'原始行情'!G3)^(12/23)-1</f>
         <v>0.07116013151287004</v>
       </c>
@@ -9948,71 +9892,71 @@
       <c r="A2" s="3">
         <v>45351</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <f>('原始行情'!E15+'原始行情'!F15)/'原始行情'!E3-1</f>
         <v>0.04222222222222238</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <f>('原始行情'!E16+'原始行情'!F16)/'原始行情'!E4-1</f>
         <v>0.0378250591016549</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <f>('原始行情'!E17+'原始行情'!F17)/'原始行情'!E5-1</f>
         <v>0.02551440329218102</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <f>('原始行情'!E18+'原始行情'!F18)/'原始行情'!E6-1</f>
         <v>0.014571948998178597</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <f>('原始行情'!E19+'原始行情'!F19)/'原始行情'!E7-1</f>
         <v>0.008169934640522847</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <f>('原始行情'!E20+'原始行情'!F20)/'原始行情'!E8-1</f>
         <v>0.020740740740740726</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <f>('原始行情'!E21+'原始行情'!F21)/'原始行情'!E9-1</f>
         <v>0.02384823848238482</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <f>('原始行情'!E22+'原始行情'!F22)/'原始行情'!E10-1</f>
         <v>0.05068664169787773</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <f>('原始行情'!E23+'原始行情'!F23)/'原始行情'!E11-1</f>
         <v>0.0650462962962961</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <f>('原始行情'!E24+'原始行情'!F24)/'原始行情'!E12-1</f>
         <v>0.06925566343042067</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="10">
         <f>('原始行情'!E25+'原始行情'!F25)/'原始行情'!E13-1</f>
         <v>0.05797979797979802</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <f>('原始行情'!E26+'原始行情'!F26)/'原始行情'!E14-1</f>
         <v>0.03874643874643868</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="10">
         <f>'原始行情'!G15/'原始行情'!G3-1</f>
         <v>0.029309999999999947</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="10">
         <f>SUMPRODUCT(B2:M2,'参数设置'!$E$4:$E$15)</f>
         <v>0.037134327253655015</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="6">
         <f>1+O2</f>
         <v>1.037134327253655</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="6">
         <f>1+N2</f>
         <v>1.02931</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="10">
         <f>P2/MAX($P$2:P2)-1</f>
         <v>0.0</v>
       </c>
@@ -10021,71 +9965,71 @@
       <c r="A3" s="3">
         <v>45382</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <f>('原始行情'!E27+'原始行情'!F27)/'原始行情'!E15-1</f>
         <v>0.030916844349680117</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <f>('原始行情'!E28+'原始行情'!F28)/'原始行情'!E16-1</f>
         <v>0.009567198177676595</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <f>('原始行情'!E29+'原始行情'!F29)/'原始行情'!E17-1</f>
         <v>-0.003611556982343611</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <f>('原始行情'!E30+'原始行情'!F30)/'原始行情'!E18-1</f>
         <v>0.01292639138240581</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <f>('原始行情'!E31+'原始行情'!F31)/'原始行情'!E19-1</f>
         <v>0.04440842787682331</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <f>('原始行情'!E32+'原始行情'!F32)/'原始行情'!E20-1</f>
         <v>0.07053701015965164</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="10">
         <f>('原始行情'!E33+'原始行情'!F33)/'原始行情'!E21-1</f>
         <v>0.04790894653255706</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="10">
         <f>('原始行情'!E34+'原始行情'!F34)/'原始行情'!E22-1</f>
         <v>0.02709125475285168</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="10">
         <f>('原始行情'!E35+'原始行情'!F35)/'原始行情'!E23-1</f>
         <v>0.013040643338404712</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="10">
         <f>('原始行情'!E36+'原始行情'!F36)/'原始行情'!E24-1</f>
         <v>0.0288539144471347</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="10">
         <f>('原始行情'!E37+'原始行情'!F37)/'原始行情'!E25-1</f>
         <v>0.05289287760168038</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <f>('原始行情'!E38+'原始行情'!F38)/'原始行情'!E26-1</f>
         <v>0.05832876211373206</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <f>'原始行情'!G27/'原始行情'!G15-1</f>
         <v>0.02671692687334226</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="10">
         <f>SUMPRODUCT(B3:M3,'参数设置'!$E$4:$E$15)</f>
         <v>0.03141661170603247</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="6">
         <f>P2*(1+O3)</f>
         <v>1.0697175736999802</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="6">
         <f>Q2*(1+N3)</f>
         <v>1.0568099999999998</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="10">
         <f>P3/MAX($P$2:P3)-1</f>
         <v>0.0</v>
       </c>
@@ -10094,71 +10038,71 @@
       <c r="A4" s="3">
         <v>45412</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <f>('原始行情'!E39+'原始行情'!F39)/'原始行情'!E27-1</f>
         <v>0.004136504653567741</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <f>('原始行情'!E40+'原始行情'!F40)/'原始行情'!E28-1</f>
         <v>-0.019855595667870096</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <f>('原始行情'!E41+'原始行情'!F41)/'原始行情'!E29-1</f>
         <v>0.002819170358437484</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <f>('原始行情'!E42+'原始行情'!F42)/'原始行情'!E30-1</f>
         <v>0.04289259127968803</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <f>('原始行情'!E43+'原始行情'!F43)/'原始行情'!E31-1</f>
         <v>0.03724394785847318</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f>('原始行情'!E44+'原始行情'!F44)/'原始行情'!E32-1</f>
         <v>0.011117136659435811</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <f>('原始行情'!E45+'原始行情'!F45)/'原始行情'!E33-1</f>
         <v>0.009345794392523255</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <f>('原始行情'!E46+'原始行情'!F46)/'原始行情'!E34-1</f>
         <v>0.04372975474317453</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <f>('原始行情'!E47+'原始行情'!F47)/'原始行情'!E35-1</f>
         <v>0.03947650718729889</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <f>('原始行情'!E48+'原始行情'!F48)/'原始行情'!E36-1</f>
         <v>0.002745636399293927</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <f>('原始行情'!E49+'原始行情'!F49)/'原始行情'!E37-1</f>
         <v>-0.009067827348567259</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <f>('原始行情'!E50+'原始行情'!F50)/'原始行情'!E38-1</f>
         <v>0.021423635107117978</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
         <f>'原始行情'!G39/'原始行情'!G27-1</f>
         <v>0.012726980251890119</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="10">
         <f>SUMPRODUCT(B4:M4,'参数设置'!$E$4:$E$15)</f>
         <v>0.01493417133421877</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="6">
         <f>P3*(1+O4)</f>
         <v>1.0856929192248406</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="6">
         <f>Q3*(1+N4)</f>
         <v>1.0702599999999998</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="10">
         <f>P4/MAX($P$2:P4)-1</f>
         <v>0.0</v>
       </c>
@@ -10167,71 +10111,71 @@
       <c r="A5" s="3">
         <v>45443</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <f>('原始行情'!E51+'原始行情'!F51)/'原始行情'!E39-1</f>
         <v>-0.023171987641606773</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <f>('原始行情'!E52+'原始行情'!F52)/'原始行情'!E40-1</f>
         <v>-0.02117863720073654</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>('原始行情'!E53+'原始行情'!F53)/'原始行情'!E41-1</f>
         <v>0.025301204819277112</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <f>('原始行情'!E54+'原始行情'!F54)/'原始行情'!E42-1</f>
         <v>0.013936097892589983</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f>('原始行情'!E55+'原始行情'!F55)/'原始行情'!E43-1</f>
         <v>-0.015260323159784761</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <f>('原始行情'!E56+'原始行情'!F56)/'原始行情'!E44-1</f>
         <v>0.02091713596138378</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <f>('原始行情'!E57+'原始行情'!F57)/'原始行情'!E45-1</f>
         <v>0.03228228228228236</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <f>('原始行情'!E58+'原始行情'!F58)/'原始行情'!E46-1</f>
         <v>-0.011527377521613702</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <f>('原始行情'!E59+'原始行情'!F59)/'原始行情'!E47-1</f>
         <v>-0.010113519091847323</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <f>('原始行情'!E60+'原始行情'!F60)/'原始行情'!E48-1</f>
         <v>0.018384510072364524</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <f>('原始行情'!E61+'原始行情'!F61)/'原始行情'!E49-1</f>
         <v>-0.01482430453879946</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <f>('原始行情'!E62+'原始行情'!F62)/'原始行情'!E50-1</f>
         <v>-0.03196887686062244</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <f>'原始行情'!G51/'原始行情'!G39-1</f>
         <v>-0.003017958253134778</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <f>SUMPRODUCT(B5:M5,'参数设置'!$E$4:$E$15)</f>
         <v>-0.0014502137279292998</v>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="6">
         <f>P4*(1+O5)</f>
         <v>1.0841184324490651</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="6">
         <f>Q4*(1+N5)</f>
         <v>1.0670299999999997</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="10">
         <f>P5/MAX($P$2:P5)-1</f>
         <v>-0.001450213727929195</v>
       </c>
@@ -10240,71 +10184,71 @@
       <c r="A6" s="3">
         <v>45473</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <f>('原始行情'!E63+'原始行情'!F63)/'原始行情'!E51-1</f>
         <v>-0.030047443331576162</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <f>('原始行情'!E64+'原始行情'!F64)/'原始行情'!E52-1</f>
         <v>0.009501411100658386</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>('原始行情'!E65+'原始行情'!F65)/'原始行情'!E53-1</f>
         <v>0.018566392479435923</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <f>('原始行情'!E66+'原始行情'!F66)/'原始行情'!E54-1</f>
         <v>-0.01521957760643633</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>('原始行情'!E67+'原始行情'!F67)/'原始行情'!E55-1</f>
         <v>0.023032512914007874</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f>('原始行情'!E68+'原始行情'!F68)/'原始行情'!E56-1</f>
         <v>0.007880220646178104</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <f>('原始行情'!E69+'原始行情'!F69)/'原始行情'!E57-1</f>
         <v>-0.01595151515151516</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <f>('原始行情'!E70+'原始行情'!F70)/'原始行情'!E58-1</f>
         <v>0.02251625925095313</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <f>('原始行情'!E71+'原始行情'!F71)/'原始行情'!E59-1</f>
         <v>-0.015929941618014976</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <f>('原始行情'!E72+'原始行情'!F72)/'原始行情'!E60-1</f>
         <v>-0.03115037449587099</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <f>('原始行情'!E73+'原始行情'!F73)/'原始行情'!E61-1</f>
         <v>0.009288500835965108</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <f>('原始行情'!E74+'原始行情'!F74)/'原始行情'!E62-1</f>
         <v>-0.027223484186615243</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <f>'原始行情'!G63/'原始行情'!G51-1</f>
         <v>-0.01029024488533592</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <f>SUMPRODUCT(B6:M6,'参数设置'!$E$4:$E$15)</f>
         <v>-0.00313782368107464</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="6">
         <f>P5*(1+O6)</f>
         <v>1.0807166599586369</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="6">
         <f>Q5*(1+N6)</f>
         <v>1.0560499999999997</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="10">
         <f>P6/MAX($P$2:P6)-1</f>
         <v>-0.004583486894025879</v>
       </c>
@@ -10313,71 +10257,71 @@
       <c r="A7" s="3">
         <v>45504</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <f>('原始行情'!E75+'原始行情'!F75)/'原始行情'!E63-1</f>
         <v>-0.02183406113537112</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <f>('原始行情'!E76+'原始行情'!F76)/'原始行情'!E64-1</f>
         <v>0.03182030884417397</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>('原始行情'!E77+'原始行情'!F77)/'原始行情'!E65-1</f>
         <v>-0.008494208494208455</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <f>('原始行情'!E78+'原始行情'!F78)/'原始行情'!E66-1</f>
         <v>0.022898154477101862</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f>('原始行情'!E79+'原始行情'!F79)/'原始行情'!E67-1</f>
         <v>0.011627906976744207</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f>('原始行情'!E80+'原始行情'!F80)/'原始行情'!E68-1</f>
         <v>-0.01307873397855086</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <f>('原始行情'!E81+'原始行情'!F81)/'原始行情'!E69-1</f>
         <v>0.02472799208704246</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <f>('原始行情'!E82+'原始行情'!F82)/'原始行情'!E70-1</f>
         <v>-0.02861545234426588</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <f>('原始行情'!E83+'原始行情'!F83)/'原始行情'!E71-1</f>
         <v>0.004891535516801326</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <f>('原始行情'!E84+'原始行情'!F84)/'原始行情'!E72-1</f>
         <v>-0.01810584958217265</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <f>('原始行情'!E85+'原始行情'!F85)/'原始行情'!E73-1</f>
         <v>-0.01791982264917802</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <f>('原始行情'!E86+'原始行情'!F86)/'原始行情'!E74-1</f>
         <v>0.015326361341507333</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <f>'原始行情'!G75/'原始行情'!G63-1</f>
         <v>-0.004138061644808344</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <f>SUMPRODUCT(B7:M7,'参数设置'!$E$4:$E$15)</f>
         <v>0.0004933093934501105</v>
       </c>
-      <c r="P7" s="12">
+      <c r="P7" s="6">
         <f>P6*(1+O7)</f>
         <v>1.0812497876386524</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="6">
         <f>Q6*(1+N7)</f>
         <v>1.05168</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="10">
         <f>P7/MAX($P$2:P7)-1</f>
         <v>-0.004092438577715352</v>
       </c>
@@ -10386,71 +10330,71 @@
       <c r="A8" s="3">
         <v>45535</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <f>('原始行情'!E87+'原始行情'!F87)/'原始行情'!E75-1</f>
         <v>-0.0306919642857143</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f>('原始行情'!E88+'原始行情'!F88)/'原始行情'!E76-1</f>
         <v>-0.008616780045351491</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f>('原始行情'!E89+'原始行情'!F89)/'原始行情'!E77-1</f>
         <v>-0.04088785046728971</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <f>('原始行情'!E90+'原始行情'!F90)/'原始行情'!E78-1</f>
         <v>-0.01069161376545269</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>('原始行情'!E91+'原始行情'!F91)/'原始行情'!E79-1</f>
         <v>-0.06601827291482454</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <f>('原始行情'!E92+'原始行情'!F92)/'原始行情'!E80-1</f>
         <v>-0.030214683275907595</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <f>('原始行情'!E93+'原始行情'!F93)/'原始行情'!E81-1</f>
         <v>-0.05791505791505791</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <f>('原始行情'!E94+'原始行情'!F94)/'原始行情'!E82-1</f>
         <v>-0.01608882846136417</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <f>('原始行情'!E95+'原始行情'!F95)/'原始行情'!E83-1</f>
         <v>-0.07492063492063494</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="10">
         <f>('原始行情'!E96+'原始行情'!F96)/'原始行情'!E84-1</f>
         <v>-0.029584599797365718</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="10">
         <f>('原始行情'!E97+'原始行情'!F97)/'原始行情'!E85-1</f>
         <v>-0.07167042889390507</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="10">
         <f>('原始行情'!E98+'原始行情'!F98)/'原始行情'!E86-1</f>
         <v>-0.03143313798614811</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="10">
         <f>'原始行情'!G87/'原始行情'!G75-1</f>
         <v>-0.04293130990415339</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="10">
         <f>SUMPRODUCT(B8:M8,'参数设置'!$E$4:$E$15)</f>
         <v>-0.0393434814115395</v>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="6">
         <f>P7*(1+O8)</f>
         <v>1.03870965671746</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="6">
         <f>Q7*(1+N8)</f>
         <v>1.00653</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="10">
         <f>P8/MAX($P$2:P8)-1</f>
         <v>-0.043274909208144696</v>
       </c>
@@ -10459,71 +10403,71 @@
       <c r="A9" s="3">
         <v>45565</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <f>('原始行情'!E99+'原始行情'!F99)/'原始行情'!E87-1</f>
         <v>0.04317789291882557</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f>('原始行情'!E100+'原始行情'!F100)/'原始行情'!E88-1</f>
         <v>0.026075022872827036</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f>('原始行情'!E101+'原始行情'!F101)/'原始行情'!E89-1</f>
         <v>0.05927730410069021</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <f>('原始行情'!E102+'原始行情'!F102)/'原始行情'!E90-1</f>
         <v>0.021952043228639084</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f>('原始行情'!E103+'原始行情'!F103)/'原始行情'!E91-1</f>
         <v>0.05837803723572099</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <f>('原始行情'!E104+'原始行情'!F104)/'原始行情'!E92-1</f>
         <v>0.010112052473353339</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <f>('原始行情'!E105+'原始行情'!F105)/'原始行情'!E93-1</f>
         <v>0.03944672131147531</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <f>('原始行情'!E106+'原始行情'!F106)/'原始行情'!E94-1</f>
         <v>-0.006678949792722211</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <f>('原始行情'!E107+'原始行情'!F107)/'原始行情'!E95-1</f>
         <v>0.04415465568519794</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="10">
         <f>('原始行情'!E108+'原始行情'!F108)/'原始行情'!E96-1</f>
         <v>0.007934850699519824</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="10">
         <f>('原始行情'!E109+'原始行情'!F109)/'原始行情'!E97-1</f>
         <v>0.060182370820668574</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="10">
         <f>('原始行情'!E110+'原始行情'!F110)/'原始行情'!E98-1</f>
         <v>0.035203520352035333</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="10">
         <f>'原始行情'!G99/'原始行情'!G87-1</f>
         <v>0.02859328584344234</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="10">
         <f>SUMPRODUCT(B9:M9,'参数设置'!$E$4:$E$15)</f>
         <v>0.03469283927183994</v>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="6">
         <f>P8*(1+O9)</f>
         <v>1.074745443888067</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="6">
         <f>Q8*(1+N9)</f>
         <v>1.03531</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="10">
         <f>P9/MAX($P$2:P9)-1</f>
         <v>-0.010083399405966254</v>
       </c>
@@ -10532,71 +10476,71 @@
       <c r="A10" s="3">
         <v>45596</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <f>('原始行情'!E111+'原始行情'!F111)/'原始行情'!E99-1</f>
         <v>0.061810154525386185</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <f>('原始行情'!E112+'原始行情'!F112)/'原始行情'!E100-1</f>
         <v>0.01783325902808741</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f>('原始行情'!E113+'原始行情'!F113)/'原始行情'!E101-1</f>
         <v>0.06324262169413553</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <f>('原始行情'!E114+'原始行情'!F114)/'原始行情'!E102-1</f>
         <v>0.034038334434897566</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f>('原始行情'!E115+'原始行情'!F115)/'原始行情'!E103-1</f>
         <v>0.03220035778175312</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <f>('原始行情'!E116+'原始行情'!F116)/'原始行情'!E104-1</f>
         <v>0.05600649350649345</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f>('原始行情'!E117+'原始行情'!F117)/'原始行情'!E105-1</f>
         <v>-0.0061606702809265945</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <f>('原始行情'!E118+'原始行情'!F118)/'原始行情'!E106-1</f>
         <v>0.049617435659633724</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <f>('原始行情'!E119+'原始行情'!F119)/'原始行情'!E107-1</f>
         <v>0.015337423312883569</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="10">
         <f>('原始行情'!E120+'原始行情'!F120)/'原始行情'!E108-1</f>
         <v>0.04640563496996042</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="10">
         <f>('原始行情'!E121+'原始行情'!F121)/'原始行情'!E109-1</f>
         <v>0.06422018348623859</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="10">
         <f>('原始行情'!E122+'原始行情'!F122)/'原始行情'!E110-1</f>
         <v>0.04268508678710581</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="10">
         <f>'原始行情'!G111/'原始行情'!G99-1</f>
         <v>0.034888101148448314</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="10">
         <f>SUMPRODUCT(B10:M10,'参数设置'!$E$4:$E$15)</f>
         <v>0.03966771802949588</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="6">
         <f>P9*(1+O10)</f>
         <v>1.1173781431097043</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="6">
         <f>Q9*(1+N10)</f>
         <v>1.0714299999999999</v>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="10">
         <f>P10/MAX($P$2:P10)-1</f>
         <v>0.0</v>
       </c>
@@ -10605,71 +10549,71 @@
       <c r="A11" s="3">
         <v>45626</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <f>('原始行情'!E123+'原始行情'!F123)/'原始行情'!E111-1</f>
         <v>0.08731808731808743</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f>('原始行情'!E124+'原始行情'!F124)/'原始行情'!E112-1</f>
         <v>0.059570740254051735</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f>('原始行情'!E125+'原始行情'!F125)/'原始行情'!E113-1</f>
         <v>0.05803893294881046</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f>('原始行情'!E126+'原始行情'!F126)/'原始行情'!E114-1</f>
         <v>0.10035155001597951</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f>('原始行情'!E127+'原始行情'!F127)/'原始行情'!E115-1</f>
         <v>0.06008087810514162</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <f>('原始行情'!E128+'原始行情'!F128)/'原始行情'!E116-1</f>
         <v>0.07993850883935427</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <f>('原始行情'!E129+'原始行情'!F129)/'原始行情'!E117-1</f>
         <v>0.06893131663773877</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <f>('原始行情'!E130+'原始行情'!F130)/'原始行情'!E118-1</f>
         <v>0.039098740888005246</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <f>('原始行情'!E131+'原始行情'!F131)/'原始行情'!E119-1</f>
         <v>0.07552870090634434</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="10">
         <f>('原始行情'!E132+'原始行情'!F132)/'原始行情'!E120-1</f>
         <v>0.10532567808354787</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="10">
         <f>('原始行情'!E133+'原始行情'!F133)/'原始行情'!E121-1</f>
         <v>0.07632902298850586</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="10">
         <f>('原始行情'!E134+'原始行情'!F134)/'原始行情'!E122-1</f>
         <v>0.12332257516561906</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="10">
         <f>'原始行情'!G123/'原始行情'!G111-1</f>
         <v>0.07077457230057016</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="10">
         <f>SUMPRODUCT(B11:M11,'参数设置'!$E$4:$E$15)</f>
         <v>0.07641388070651696</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="6">
         <f>P10*(1+O11)</f>
         <v>1.2027613432413586</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="6">
         <f>Q10*(1+N11)</f>
         <v>1.1472599999999997</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="10">
         <f>P11/MAX($P$2:P11)-1</f>
         <v>0.0</v>
       </c>
@@ -10678,71 +10622,71 @@
       <c r="A12" s="3">
         <v>45657</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <f>('原始行情'!E135+'原始行情'!F135)/'原始行情'!E123-1</f>
         <v>0.02390057361376674</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f>('原始行情'!E136+'原始行情'!F136)/'原始行情'!E124-1</f>
         <v>0.023563455973542702</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>('原始行情'!E137+'原始行情'!F137)/'原始行情'!E125-1</f>
         <v>-0.019761499148211348</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f>('原始行情'!E138+'原始行情'!F138)/'原始行情'!E126-1</f>
         <v>-0.005227998838222447</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f>('原始行情'!E139+'原始行情'!F139)/'原始行情'!E127-1</f>
         <v>0.020980926430517632</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f>('原始行情'!E140+'原始行情'!F140)/'原始行情'!E128-1</f>
         <v>-0.008066429418742471</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <f>('原始行情'!E141+'原始行情'!F141)/'原始行情'!E129-1</f>
         <v>-0.016933426119229766</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <f>('原始行情'!E142+'原始行情'!F142)/'原始行情'!E130-1</f>
         <v>0.030824829931972886</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f>('原始行情'!E143+'原始行情'!F143)/'原始行情'!E131-1</f>
         <v>0.024478330658106007</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <f>('原始行情'!E144+'原始行情'!F144)/'原始行情'!E132-1</f>
         <v>-0.004836109618484574</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="10">
         <f>('原始行情'!E145+'原始行情'!F145)/'原始行情'!E133-1</f>
         <v>0.025362923410645832</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <f>('原始行情'!E146+'原始行情'!F146)/'原始行情'!E134-1</f>
         <v>0.044457885982156276</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="10">
         <f>'原始行情'!G135/'原始行情'!G123-1</f>
         <v>0.004584836915781931</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="10">
         <f>SUMPRODUCT(B12:M12,'参数设置'!$E$4:$E$15)</f>
         <v>0.011142814611335518</v>
       </c>
-      <c r="P12" s="12">
+      <c r="P12" s="6">
         <f>P11*(1+O12)</f>
         <v>1.216163489910778</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="6">
         <f>Q11*(1+N12)</f>
         <v>1.1525199999999998</v>
       </c>
-      <c r="R12" s="11">
+      <c r="R12" s="10">
         <f>P12/MAX($P$2:P12)-1</f>
         <v>0.0</v>
       </c>
@@ -10751,71 +10695,71 @@
       <c r="A13" s="3">
         <v>45688</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <f>('原始行情'!E147+'原始行情'!F147)/'原始行情'!E135-1</f>
         <v>-0.016806722689075793</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f>('原始行情'!E148+'原始行情'!F148)/'原始行情'!E136-1</f>
         <v>0.005250403877221199</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f>('原始行情'!E149+'原始行情'!F149)/'原始行情'!E137-1</f>
         <v>-0.014250955856795255</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <f>('原始行情'!E150+'原始行情'!F150)/'原始行情'!E138-1</f>
         <v>-0.04759124087591249</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f>('原始行情'!E151+'原始行情'!F151)/'原始行情'!E139-1</f>
         <v>-0.04296770749933276</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <f>('原始行情'!E152+'原始行情'!F152)/'原始行情'!E140-1</f>
         <v>-0.005740253527864225</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <f>('原始行情'!E153+'原始行情'!F153)/'原始行情'!E141-1</f>
         <v>0.0108541764983483</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="10">
         <f>('原始行情'!E154+'原始行情'!F154)/'原始行情'!E142-1</f>
         <v>-0.017941843679109226</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <f>('原始行情'!E155+'原始行情'!F155)/'原始行情'!E143-1</f>
         <v>-0.024676850763807434</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <f>('原始行情'!E156+'原始行情'!F156)/'原始行情'!E144-1</f>
         <v>0.007739380849532074</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="10">
         <f>('原始行情'!E157+'原始行情'!F157)/'原始行情'!E145-1</f>
         <v>0.015296989422294516</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <f>('原始行情'!E158+'原始行情'!F158)/'原始行情'!E146-1</f>
         <v>-0.021282756623715038</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="10">
         <f>'原始行情'!G147/'原始行情'!G135-1</f>
         <v>-0.01832506160413694</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="10">
         <f>SUMPRODUCT(B13:M13,'参数设置'!$E$4:$E$15)</f>
         <v>-0.012866339018591872</v>
       </c>
-      <c r="P13" s="12">
+      <c r="P13" s="6">
         <f>P12*(1+O13)</f>
         <v>1.2005159181475522</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="Q13" s="6">
         <f>Q12*(1+N13)</f>
         <v>1.1314</v>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="10">
         <f>P13/MAX($P$2:P13)-1</f>
         <v>-0.0128663390185918</v>
       </c>
@@ -10824,71 +10768,71 @@
       <c r="A14" s="3">
         <v>45716</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <f>('原始行情'!E159+'原始行情'!F159)/'原始行情'!E147-1</f>
         <v>-0.04700854700854695</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f>('原始行情'!E160+'原始行情'!F160)/'原始行情'!E148-1</f>
         <v>-0.029329047810365605</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f>('原始行情'!E161+'原始行情'!F161)/'原始行情'!E149-1</f>
         <v>-0.013046544428772955</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <f>('原始行情'!E162+'原始行情'!F162)/'原始行情'!E150-1</f>
         <v>-0.019926425505824574</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f>('原始行情'!E163+'原始行情'!F163)/'原始行情'!E151-1</f>
         <v>-0.047964305633017235</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <f>('原始行情'!E164+'原始行情'!F164)/'原始行情'!E152-1</f>
         <v>-0.060861197979312</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <f>('原始行情'!E165+'原始行情'!F165)/'原始行情'!E153-1</f>
         <v>-0.024276377217553824</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="10">
         <f>('原始行情'!E166+'原始行情'!F166)/'原始行情'!E154-1</f>
         <v>0.0031499370012599837</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <f>('原始行情'!E167+'原始行情'!F167)/'原始行情'!E155-1</f>
         <v>0.009236947791164685</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <f>('原始行情'!E168+'原始行情'!F168)/'原始行情'!E156-1</f>
         <v>-0.010358992677263923</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="10">
         <f>('原始行情'!E169+'原始行情'!F169)/'原始行情'!E157-1</f>
         <v>-0.044077576534701124</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="10">
         <f>('原始行情'!E170+'原始行情'!F170)/'原始行情'!E158-1</f>
         <v>-0.06168639053254432</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="10">
         <f>'原始行情'!G159/'原始行情'!G147-1</f>
         <v>-0.03127983029874504</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="10">
         <f>SUMPRODUCT(B14:M14,'参数设置'!$E$4:$E$15)</f>
         <v>-0.02857961496630279</v>
       </c>
-      <c r="P14" s="12">
+      <c r="P14" s="6">
         <f>P13*(1+O14)</f>
         <v>1.1662056354459778</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="6">
         <f>Q13*(1+N14)</f>
         <v>1.09601</v>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="10">
         <f>P14/MAX($P$2:P14)-1</f>
         <v>-0.041078238969717296</v>
       </c>
@@ -10897,71 +10841,71 @@
       <c r="A15" s="3">
         <v>45747</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <f>('原始行情'!E171+'原始行情'!F171)/'原始行情'!E159-1</f>
         <v>-0.05331340308918786</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f>('原始行情'!E172+'原始行情'!F172)/'原始行情'!E160-1</f>
         <v>-0.05173841059602646</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f>('原始行情'!E173+'原始行情'!F173)/'原始行情'!E161-1</f>
         <v>-0.03644158628081451</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <f>('原始行情'!E174+'原始行情'!F174)/'原始行情'!E162-1</f>
         <v>-0.01563966218329682</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f>('原始行情'!E175+'原始行情'!F175)/'原始行情'!E163-1</f>
         <v>-0.005272407732864637</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <f>('原始行情'!E176+'原始行情'!F176)/'原始行情'!E164-1</f>
         <v>-0.0023053278688524026</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <f>('原始行情'!E177+'原始行情'!F177)/'原始行情'!E165-1</f>
         <v>0.00645933014354072</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="10">
         <f>('原始行情'!E178+'原始行情'!F178)/'原始行情'!E166-1</f>
         <v>-0.012978857023236423</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <f>('原始行情'!E179+'原始行情'!F179)/'原始行情'!E167-1</f>
         <v>-0.03621169916434541</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="10">
         <f>('原始行情'!E180+'原始行情'!F180)/'原始行情'!E168-1</f>
         <v>-0.04620104674246517</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="10">
         <f>('原始行情'!E181+'原始行情'!F181)/'原始行情'!E169-1</f>
         <v>-0.04493628437290409</v>
       </c>
-      <c r="M15" s="11">
+      <c r="M15" s="10">
         <f>('原始行情'!E182+'原始行情'!F182)/'原始行情'!E170-1</f>
         <v>-0.03531451994324453</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="10">
         <f>'原始行情'!G171/'原始行情'!G159-1</f>
         <v>-0.02753624510725272</v>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="10">
         <f>SUMPRODUCT(B15:M15,'参数设置'!$E$4:$E$15)</f>
         <v>-0.02817391571200374</v>
       </c>
-      <c r="P15" s="12">
+      <c r="P15" s="6">
         <f>P14*(1+O15)</f>
         <v>1.133349056170059</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="6">
         <f>Q14*(1+N15)</f>
         <v>1.0658299999999998</v>
       </c>
-      <c r="R15" s="11">
+      <c r="R15" s="10">
         <f>P15/MAX($P$2:P15)-1</f>
         <v>-0.0680948198393907</v>
       </c>
@@ -10970,71 +10914,71 @@
       <c r="A16" s="3">
         <v>45777</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <f>('原始行情'!E183+'原始行情'!F183)/'原始行情'!E171-1</f>
         <v>-0.07210526315789478</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f>('原始行情'!E184+'原始行情'!F184)/'原始行情'!E172-1</f>
         <v>-0.08206023570493226</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f>('原始行情'!E185+'原始行情'!F185)/'原始行情'!E173-1</f>
         <v>-0.08602150537634412</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <f>('原始行情'!E186+'原始行情'!F186)/'原始行情'!E174-1</f>
         <v>-0.08579599618684464</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f>('原始行情'!E187+'原始行情'!F187)/'原始行情'!E175-1</f>
         <v>-0.08745583038869265</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <f>('原始行情'!E188+'原始行情'!F188)/'原始行情'!E176-1</f>
         <v>-0.08395378690629018</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="10">
         <f>('原始行情'!E189+'原始行情'!F189)/'原始行情'!E177-1</f>
         <v>-0.035179462800094985</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="10">
         <f>('原始行情'!E190+'原始行情'!F190)/'原始行情'!E178-1</f>
         <v>-0.03520678685047718</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <f>('原始行情'!E191+'原始行情'!F191)/'原始行情'!E179-1</f>
         <v>-0.04314616019818329</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <f>('原始行情'!E192+'原始行情'!F192)/'原始行情'!E180-1</f>
         <v>-0.048817407757805076</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="10">
         <f>('原始行情'!E193+'原始行情'!F193)/'原始行情'!E181-1</f>
         <v>-0.0563553370786517</v>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="10">
         <f>('原始行情'!E194+'原始行情'!F194)/'原始行情'!E182-1</f>
         <v>-0.06487988233371467</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="10">
         <f>'原始行情'!G183/'原始行情'!G171-1</f>
         <v>-0.06409089629678277</v>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="10">
         <f>SUMPRODUCT(B16:M16,'参数设置'!$E$4:$E$15)</f>
         <v>-0.06571119226883793</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P16" s="6">
         <f>P15*(1+O16)</f>
         <v>1.0588753384323621</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="Q16" s="6">
         <f>Q15*(1+N16)</f>
         <v>0.9975199999999999</v>
       </c>
-      <c r="R16" s="11">
+      <c r="R16" s="10">
         <f>P16/MAX($P$2:P16)-1</f>
         <v>-0.1293314203092506</v>
       </c>
@@ -11043,71 +10987,71 @@
       <c r="A17" s="3">
         <v>45808</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <f>('原始行情'!E195+'原始行情'!F195)/'原始行情'!E183-1</f>
         <v>0.00340328984685212</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <f>('原始行情'!E196+'原始行情'!F196)/'原始行情'!E184-1</f>
         <v>0.011887779362814932</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f>('原始行情'!E197+'原始行情'!F197)/'原始行情'!E185-1</f>
         <v>0.021095334685598433</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <f>('原始行情'!E198+'原始行情'!F198)/'原始行情'!E186-1</f>
         <v>0.029892248870351024</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f>('原始行情'!E199+'原始行情'!F199)/'原始行情'!E187-1</f>
         <v>0.0319457889641821</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <f>('原始行情'!E200+'原始行情'!F200)/'原始行情'!E188-1</f>
         <v>0.03587443946188351</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <f>('原始行情'!E201+'原始行情'!F201)/'原始行情'!E189-1</f>
         <v>0.025868440502586854</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <f>('原始行情'!E202+'原始行情'!F202)/'原始行情'!E190-1</f>
         <v>0.023961310178061135</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <f>('原始行情'!E203+'原始行情'!F203)/'原始行情'!E191-1</f>
         <v>0.015965480043149904</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <f>('原始行情'!E204+'原始行情'!F204)/'原始行情'!E192-1</f>
         <v>0.013526954445991723</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="10">
         <f>('原始行情'!E205+'原始行情'!F205)/'原始行情'!E193-1</f>
         <v>0.013023255813953583</v>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="10">
         <f>('原始行情'!E206+'原始行情'!F206)/'原始行情'!E194-1</f>
         <v>0.015728766165676422</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="10">
         <f>'原始行情'!G195/'原始行情'!G183-1</f>
         <v>0.014475900232576944</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="10">
         <f>SUMPRODUCT(B17:M17,'参数设置'!$E$4:$E$15)</f>
         <v>0.01990953804549747</v>
       </c>
-      <c r="P17" s="12">
+      <c r="P17" s="6">
         <f>P16*(1+O17)</f>
         <v>1.0799570572683201</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="Q17" s="6">
         <f>Q16*(1+N17)</f>
         <v>1.01196</v>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="10">
         <f>P17/MAX($P$2:P17)-1</f>
         <v>-0.11199681109687853</v>
       </c>
@@ -11116,71 +11060,71 @@
       <c r="A18" s="3">
         <v>45838</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <f>('原始行情'!E207+'原始行情'!F207)/'原始行情'!E195-1</f>
         <v>0.0418315432447709</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <f>('原始行情'!E208+'原始行情'!F208)/'原始行情'!E196-1</f>
         <v>0.05836466165413512</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f>('原始行情'!E209+'原始行情'!F209)/'原始行情'!E197-1</f>
         <v>0.07127532777115597</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <f>('原始行情'!E210+'原始行情'!F210)/'原始行情'!E198-1</f>
         <v>0.07883901451231856</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f>('原始行情'!E211+'原始行情'!F211)/'原始行情'!E199-1</f>
         <v>0.0752970606629142</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <f>('原始行情'!E212+'原始行情'!F212)/'原始行情'!E200-1</f>
         <v>0.07007575757575757</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="10">
         <f>('原始行情'!E213+'原始行情'!F213)/'原始行情'!E201-1</f>
         <v>0.03847262247838623</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="10">
         <f>('原始行情'!E214+'原始行情'!F214)/'原始行情'!E202-1</f>
         <v>0.027565478746243155</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="10">
         <f>('原始行情'!E215+'原始行情'!F215)/'原始行情'!E203-1</f>
         <v>0.013930770864302389</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="10">
         <f>('原始行情'!E216+'原始行情'!F216)/'原始行情'!E204-1</f>
         <v>0.008792934249264084</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="10">
         <f>('原始行情'!E217+'原始行情'!F217)/'原始行情'!E205-1</f>
         <v>0.009733700642791554</v>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="10">
         <f>('原始行情'!E218+'原始行情'!F218)/'原始行情'!E206-1</f>
         <v>0.017412250516173566</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="10">
         <f>'原始行情'!G207/'原始行情'!G195-1</f>
         <v>0.03126605794695436</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="10">
         <f>SUMPRODUCT(B18:M18,'参数设置'!$E$4:$E$15)</f>
         <v>0.043947961278318</v>
       </c>
-      <c r="P18" s="12">
+      <c r="P18" s="6">
         <f>P17*(1+O18)</f>
         <v>1.1274189682033946</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="6">
         <f>Q17*(1+N18)</f>
         <v>1.0435999999999999</v>
       </c>
-      <c r="R18" s="11">
+      <c r="R18" s="10">
         <f>P18/MAX($P$2:P18)-1</f>
         <v>-0.0729708813359412</v>
       </c>
@@ -11189,71 +11133,71 @@
       <c r="A19" s="3">
         <v>45869</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <f>('原始行情'!E219+'原始行情'!F219)/'原始行情'!E207-1</f>
         <v>0.05340599455040862</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <f>('原始行情'!E220+'原始行情'!F220)/'原始行情'!E208-1</f>
         <v>0.05884975479268828</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f>('原始行情'!E221+'原始行情'!F221)/'原始行情'!E209-1</f>
         <v>0.05212211466865235</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <f>('原始行情'!E222+'原始行情'!F222)/'原始行情'!E210-1</f>
         <v>0.040188383045525855</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <f>('原始行情'!E223+'原始行情'!F223)/'原始行情'!E211-1</f>
         <v>0.02772913018096923</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="10">
         <f>('原始行情'!E224+'原始行情'!F224)/'原始行情'!E212-1</f>
         <v>0.03044912458766813</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="10">
         <f>('原始行情'!E225+'原始行情'!F225)/'原始行情'!E213-1</f>
         <v>0.019262009747041065</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="10">
         <f>('原始行情'!E226+'原始行情'!F226)/'原始行情'!E214-1</f>
         <v>0.03710691823899359</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="10">
         <f>('原始行情'!E227+'原始行情'!F227)/'原始行情'!E215-1</f>
         <v>0.04645785158713478</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="10">
         <f>('原始行情'!E228+'原始行情'!F228)/'原始行情'!E216-1</f>
         <v>0.051552431165788004</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="10">
         <f>('原始行情'!E229+'原始行情'!F229)/'原始行情'!E217-1</f>
         <v>0.04728002920773999</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="10">
         <f>('原始行情'!E230+'原始行情'!F230)/'原始行情'!E218-1</f>
         <v>0.03954514596062464</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="10">
         <f>'原始行情'!G219/'原始行情'!G207-1</f>
         <v>0.03351858949789199</v>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="10">
         <f>SUMPRODUCT(B19:M19,'参数设置'!$E$4:$E$15)</f>
         <v>0.04226941513310616</v>
       </c>
-      <c r="P19" s="12">
+      <c r="P19" s="6">
         <f>P18*(1+O19)</f>
         <v>1.1750743085993223</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="6">
         <f>Q18*(1+N19)</f>
         <v>1.0785799999999999</v>
       </c>
-      <c r="R19" s="11">
+      <c r="R19" s="10">
         <f>P19/MAX($P$2:P19)-1</f>
         <v>-0.033785902678652335</v>
       </c>
@@ -11262,71 +11206,71 @@
       <c r="A20" s="3">
         <v>45900</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <f>('原始行情'!E231+'原始行情'!F231)/'原始行情'!E219-1</f>
         <v>0.04500775995861361</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <f>('原始行情'!E232+'原始行情'!F232)/'原始行情'!E220-1</f>
         <v>0.027789473684210586</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f>('原始行情'!E233+'原始行情'!F233)/'原始行情'!E221-1</f>
         <v>0.013446567586695046</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <f>('原始行情'!E234+'原始行情'!F234)/'原始行情'!E222-1</f>
         <v>0.02263809236341685</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <f>('原始行情'!E235+'原始行情'!F235)/'原始行情'!E223-1</f>
         <v>0.04288554387957966</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <f>('原始行情'!E236+'原始行情'!F236)/'原始行情'!E224-1</f>
         <v>0.0554050726422064</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="10">
         <f>('原始行情'!E237+'原始行情'!F237)/'原始行情'!E225-1</f>
         <v>0.024590163934426146</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="10">
         <f>('原始行情'!E238+'原始行情'!F238)/'原始行情'!E226-1</f>
         <v>-0.0016171417020416357</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <f>('原始行情'!E239+'原始行情'!F239)/'原始行情'!E227-1</f>
         <v>-0.013057452792285984</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <f>('原始行情'!E240+'原始行情'!F240)/'原始行情'!E228-1</f>
         <v>0.011142061281337101</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <f>('原始行情'!E241+'原始行情'!F241)/'原始行情'!E229-1</f>
         <v>0.04566846784033474</v>
       </c>
-      <c r="M20" s="11">
+      <c r="M20" s="10">
         <f>('原始行情'!E242+'原始行情'!F242)/'原始行情'!E230-1</f>
         <v>0.0605714285714285</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="10">
         <f>'原始行情'!G231/'原始行情'!G219-1</f>
         <v>0.02173227762428387</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="10">
         <f>SUMPRODUCT(B20:M20,'参数设置'!$E$4:$E$15)</f>
         <v>0.0276081557207723</v>
       </c>
-      <c r="P20" s="12">
+      <c r="P20" s="6">
         <f>P19*(1+O20)</f>
         <v>1.2075159430946112</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="6">
         <f>Q19*(1+N20)</f>
         <v>1.10202</v>
       </c>
-      <c r="R20" s="11">
+      <c r="R20" s="10">
         <f>P20/MAX($P$2:P20)-1</f>
         <v>-0.007110513420199194</v>
       </c>
@@ -11335,71 +11279,71 @@
       <c r="A21" s="3">
         <v>45930</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <f>('原始行情'!E243+'原始行情'!F243)/'原始行情'!E231-1</f>
         <v>0.05297029702970302</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <f>('原始行情'!E244+'原始行情'!F244)/'原始行情'!E232-1</f>
         <v>0.03277345350266292</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f>('原始行情'!E245+'原始行情'!F245)/'原始行情'!E233-1</f>
         <v>0.05307262569832405</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="10">
         <f>('原始行情'!E246+'原始行情'!F246)/'原始行情'!E234-1</f>
         <v>0.08618654073199505</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <f>('原始行情'!E247+'原始行情'!F247)/'原始行情'!E235-1</f>
         <v>0.07135076252723316</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="10">
         <f>('原始行情'!E248+'原始行情'!F248)/'原始行情'!E236-1</f>
         <v>0.039897340177321494</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="10">
         <f>('原始行情'!E249+'原始行情'!F249)/'原始行情'!E237-1</f>
         <v>0.01333333333333342</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="10">
         <f>('原始行情'!E250+'原始行情'!F250)/'原始行情'!E238-1</f>
         <v>0.05365458594857264</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <f>('原始行情'!E251+'原始行情'!F251)/'原始行情'!E239-1</f>
         <v>0.05923061266028906</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="10">
         <f>('原始行情'!E252+'原始行情'!F252)/'原始行情'!E240-1</f>
         <v>0.03783287419651038</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="10">
         <f>('原始行情'!E253+'原始行情'!F253)/'原始行情'!E241-1</f>
         <v>0.04517419569928327</v>
       </c>
-      <c r="M21" s="11">
+      <c r="M21" s="10">
         <f>('原始行情'!E254+'原始行情'!F254)/'原始行情'!E242-1</f>
         <v>0.0905172413793105</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="10">
         <f>'原始行情'!G243/'原始行情'!G231-1</f>
         <v>0.04907351953685035</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="10">
         <f>SUMPRODUCT(B21:M21,'参数设置'!$E$4:$E$15)</f>
         <v>0.05249246842142453</v>
       </c>
-      <c r="P21" s="12">
+      <c r="P21" s="6">
         <f>P20*(1+O21)</f>
         <v>1.2709014356058717</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="Q21" s="6">
         <f>Q20*(1+N21)</f>
         <v>1.1561</v>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="10">
         <f>P21/MAX($P$2:P21)-1</f>
         <v>0.0</v>
       </c>
@@ -11408,71 +11352,71 @@
       <c r="A22" s="3">
         <v>45961</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <f>('原始行情'!E255+'原始行情'!F255)/'原始行情'!E243-1</f>
         <v>-0.005171603196991059</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <f>('原始行情'!E256+'原始行情'!F256)/'原始行情'!E244-1</f>
         <v>-0.010313367711225818</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f>('原始行情'!E257+'原始行情'!F257)/'原始行情'!E245-1</f>
         <v>0.023872679045092715</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <f>('原始行情'!E258+'原始行情'!F258)/'原始行情'!E246-1</f>
         <v>-0.001630434782608603</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <f>('原始行情'!E259+'原始行情'!F259)/'原始行情'!E247-1</f>
         <v>-0.04016268429079828</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="10">
         <f>('原始行情'!E260+'原始行情'!F260)/'原始行情'!E248-1</f>
         <v>-0.00830154812654249</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="10">
         <f>('原始行情'!E261+'原始行情'!F261)/'原始行情'!E249-1</f>
         <v>0.005921052631578938</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="10">
         <f>('原始行情'!E262+'原始行情'!F262)/'原始行情'!E250-1</f>
         <v>-0.031129900076863892</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="10">
         <f>('原始行情'!E263+'原始行情'!F263)/'原始行情'!E251-1</f>
         <v>-0.01633358954650277</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="10">
         <f>('原始行情'!E264+'原始行情'!F264)/'原始行情'!E252-1</f>
         <v>0.022119978764820303</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="10">
         <f>('原始行情'!E265+'原始行情'!F265)/'原始行情'!E253-1</f>
         <v>-0.0043062200956938135</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="10">
         <f>('原始行情'!E266+'原始行情'!F266)/'原始行情'!E254-1</f>
         <v>-0.014539808018068867</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="10">
         <f>'原始行情'!G255/'原始行情'!G243-1</f>
         <v>-0.008459475823890616</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="10">
         <f>SUMPRODUCT(B22:M22,'参数设置'!$E$4:$E$15)</f>
         <v>-0.006462350335248799</v>
       </c>
-      <c r="P22" s="12">
+      <c r="P22" s="6">
         <f>P21*(1+O22)</f>
         <v>1.262688425287416</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="6">
         <f>Q21*(1+N22)</f>
         <v>1.14632</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="10">
         <f>P22/MAX($P$2:P22)-1</f>
         <v>-0.006462350335248668</v>
       </c>
@@ -11481,71 +11425,71 @@
       <c r="A23" s="3">
         <v>45991</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <f>('原始行情'!E267+'原始行情'!F267)/'原始行情'!E255-1</f>
         <v>-0.018431001890359178</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <f>('原始行情'!E268+'原始行情'!F268)/'原始行情'!E256-1</f>
         <v>0.010420841683366877</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f>('原始行情'!E269+'原始行情'!F269)/'原始行情'!E257-1</f>
         <v>0.007124352331606243</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="10">
         <f>('原始行情'!E270+'原始行情'!F270)/'原始行情'!E258-1</f>
         <v>-0.03565596080566147</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="10">
         <f>('原始行情'!E271+'原始行情'!F271)/'原始行情'!E259-1</f>
         <v>-0.0010593220338982468</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="10">
         <f>('原始行情'!E272+'原始行情'!F272)/'原始行情'!E260-1</f>
         <v>-0.01628959276018116</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="10">
         <f>('原始行情'!E273+'原始行情'!F273)/'原始行情'!E261-1</f>
         <v>-0.03161107477654235</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="10">
         <f>('原始行情'!E274+'原始行情'!F274)/'原始行情'!E262-1</f>
         <v>0.018445061483538305</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="10">
         <f>('原始行情'!E275+'原始行情'!F275)/'原始行情'!E263-1</f>
         <v>-0.009962883375659315</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="10">
         <f>('原始行情'!E276+'原始行情'!F276)/'原始行情'!E264-1</f>
         <v>-0.012292243767313082</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="10">
         <f>('原始行情'!E277+'原始行情'!F277)/'原始行情'!E265-1</f>
         <v>0.031234983181162912</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="10">
         <f>('原始行情'!E278+'原始行情'!F278)/'原始行情'!E266-1</f>
         <v>-0.009024495058014503</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="10">
         <f>'原始行情'!G267/'原始行情'!G255-1</f>
         <v>-0.008461860562495649</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="10">
         <f>SUMPRODUCT(B23:M23,'参数设置'!$E$4:$E$15)</f>
         <v>-0.005440672089627106</v>
       </c>
-      <c r="P23" s="12">
+      <c r="P23" s="6">
         <f>P22*(1+O23)</f>
         <v>1.2558185516140596</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="6">
         <f>Q22*(1+N23)</f>
         <v>1.13662</v>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="10">
         <f>P23/MAX($P$2:P23)-1</f>
         <v>-0.011867862895773351</v>
       </c>
@@ -11554,71 +11498,71 @@
       <c r="A24" s="3">
         <v>46022</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <f>('原始行情'!E279+'原始行情'!F279)/'原始行情'!E267-1</f>
         <v>-0.012999518536350507</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <f>('原始行情'!E280+'原始行情'!F280)/'原始行情'!E268-1</f>
         <v>0.029750099166997224</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f>('原始行情'!E281+'原始行情'!F281)/'原始行情'!E269-1</f>
         <v>-0.019935691318327953</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="10">
         <f>('原始行情'!E282+'原始行情'!F282)/'原始行情'!E270-1</f>
         <v>0.009031893875246944</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <f>('原始行情'!E283+'原始行情'!F283)/'原始行情'!E271-1</f>
         <v>-0.0015906680805939377</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="10">
         <f>('原始行情'!E284+'原始行情'!F284)/'原始行情'!E272-1</f>
         <v>-0.015869365225390952</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="10">
         <f>('原始行情'!E285+'原始行情'!F285)/'原始行情'!E273-1</f>
         <v>0.027239981990094586</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="10">
         <f>('原始行情'!E286+'原始行情'!F286)/'原始行情'!E274-1</f>
         <v>-0.012852969814995174</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="10">
         <f>('原始行情'!E287+'原始行情'!F287)/'原始行情'!E275-1</f>
         <v>0.032754538279400336</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="10">
         <f>('原始行情'!E288+'原始行情'!F288)/'原始行情'!E276-1</f>
         <v>0.012094653812445344</v>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="10">
         <f>('原始行情'!E289+'原始行情'!F289)/'原始行情'!E277-1</f>
         <v>0.014756135445790575</v>
       </c>
-      <c r="M24" s="11">
+      <c r="M24" s="10">
         <f>('原始行情'!E290+'原始行情'!F290)/'原始行情'!E278-1</f>
         <v>0.037583116507660996</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="10">
         <f>'原始行情'!G279/'原始行情'!G267-1</f>
         <v>0.003703964385634695</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="10">
         <f>SUMPRODUCT(B24:M24,'参数设置'!$E$4:$E$15)</f>
         <v>0.007554182370882454</v>
       </c>
-      <c r="P24" s="12">
+      <c r="P24" s="6">
         <f>P23*(1+O24)</f>
         <v>1.2653052339776898</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="6">
         <f>Q23*(1+N24)</f>
         <v>1.14083</v>
       </c>
-      <c r="R24" s="11">
+      <c r="R24" s="10">
         <f>P24/MAX($P$2:P24)-1</f>
         <v>-0.004403332525558135</v>
       </c>
@@ -11727,15 +11671,15 @@
       <c r="J4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="9">
         <f>SUM(G5:G16)</f>
         <v>-523000.0</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <f>K4/'参数设置'!$B$3</f>
         <v>-0.0523</v>
       </c>
-      <c r="M4" s="14" t="str">
+      <c r="M4" s="4" t="str">
         <f>IF(L4&lt;=-15%,"高风险",IF(L4&lt;0,"中风险","正向情景"))</f>
         <v>中风险</v>
       </c>
@@ -11750,34 +11694,34 @@
       <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>'参数设置'!E4</f>
         <v>0.1</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <f>'参数设置'!B22</f>
         <v>-0.08</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="9">
         <f>D5*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="9">
         <f>E5*F5</f>
         <v>-80000.0</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="9">
         <f>SUM(G17:G28)</f>
         <v>-1676000.0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <f>K5/'参数设置'!$B$3</f>
         <v>-0.1676</v>
       </c>
-      <c r="M5" s="14" t="str">
+      <c r="M5" s="4" t="str">
         <f>IF(L5&lt;=-15%,"高风险",IF(L5&lt;0,"中风险","正向情景"))</f>
         <v>高风险</v>
       </c>
@@ -11792,34 +11736,34 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>'参数设置'!E5</f>
         <v>0.09</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <f>'参数设置'!B22</f>
         <v>-0.08</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="9">
         <f>D6*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="9">
         <f>E6*F6</f>
         <v>-72000.0</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="9">
         <f>SUM(G29:G40)</f>
         <v>986000.0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <f>K6/'参数设置'!$B$3</f>
         <v>0.0986</v>
       </c>
-      <c r="M6" s="14" t="str">
+      <c r="M6" s="4" t="str">
         <f>IF(L6&lt;=-15%,"高风险",IF(L6&lt;0,"中风险","正向情景"))</f>
         <v>正向情景</v>
       </c>
@@ -11834,19 +11778,19 @@
       <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>'参数设置'!E6</f>
         <v>0.1</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <f>'参数设置'!B23</f>
         <v>-0.05</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="9">
         <f>D7*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="9">
         <f>E7*F7</f>
         <v>-50000.0</v>
       </c>
@@ -11861,19 +11805,19 @@
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f>'参数设置'!E7</f>
         <v>0.08</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <f>'参数设置'!B23</f>
         <v>-0.05</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="9">
         <f>D8*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="9">
         <f>E8*F8</f>
         <v>-40000.0</v>
       </c>
@@ -11888,19 +11832,19 @@
       <c r="C9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f>'参数设置'!E8</f>
         <v>0.09</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <f>'参数设置'!B24</f>
         <v>-0.03</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="9">
         <f>D9*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="9">
         <f>E9*F9</f>
         <v>-27000.0</v>
       </c>
@@ -11915,19 +11859,19 @@
       <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f>'参数设置'!E9</f>
         <v>0.07</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <f>'参数设置'!B24</f>
         <v>-0.03</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="9">
         <f>D10*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="9">
         <f>E10*F10</f>
         <v>-21000.000000000004</v>
       </c>
@@ -11942,19 +11886,19 @@
       <c r="C11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f>'参数设置'!E10</f>
         <v>0.09</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f>'参数设置'!B25</f>
         <v>-0.04</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="9">
         <f>D11*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="9">
         <f>E11*F11</f>
         <v>-36000.0</v>
       </c>
@@ -11969,19 +11913,19 @@
       <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>'参数设置'!E11</f>
         <v>0.08</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f>'参数设置'!B25</f>
         <v>-0.04</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="9">
         <f>D12*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="9">
         <f>E12*F12</f>
         <v>-32000.0</v>
       </c>
@@ -11996,19 +11940,19 @@
       <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f>'参数设置'!E12</f>
         <v>0.08</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <f>'参数设置'!B26</f>
         <v>-0.06</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="9">
         <f>D13*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="9">
         <f>E13*F13</f>
         <v>-48000.0</v>
       </c>
@@ -12023,19 +11967,19 @@
       <c r="C14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f>'参数设置'!E13</f>
         <v>0.07</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <f>'参数设置'!B26</f>
         <v>-0.06</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="9">
         <f>D14*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="9">
         <f>E14*F14</f>
         <v>-42000.00000000001</v>
       </c>
@@ -12050,19 +11994,19 @@
       <c r="C15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f>'参数设置'!E14</f>
         <v>0.08</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <f>'参数设置'!B27</f>
         <v>-0.05</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="9">
         <f>D15*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="9">
         <f>E15*F15</f>
         <v>-40000.0</v>
       </c>
@@ -12077,19 +12021,19 @@
       <c r="C16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f>'参数设置'!E15</f>
         <v>0.07</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <f>'参数设置'!B27</f>
         <v>-0.05</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="9">
         <f>D16*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="9">
         <f>E16*F16</f>
         <v>-35000.00000000001</v>
       </c>
@@ -12104,19 +12048,19 @@
       <c r="C17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f>'参数设置'!E4</f>
         <v>0.1</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <f>'参数设置'!C22</f>
         <v>-0.18</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="9">
         <f>D17*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="9">
         <f>E17*F17</f>
         <v>-180000.0</v>
       </c>
@@ -12131,19 +12075,19 @@
       <c r="C18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f>'参数设置'!E5</f>
         <v>0.09</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <f>'参数设置'!C22</f>
         <v>-0.18</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="9">
         <f>D18*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="9">
         <f>E18*F18</f>
         <v>-162000.0</v>
       </c>
@@ -12158,19 +12102,19 @@
       <c r="C19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f>'参数设置'!E6</f>
         <v>0.1</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <f>'参数设置'!C23</f>
         <v>-0.22</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="9">
         <f>D19*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="9">
         <f>E19*F19</f>
         <v>-220000.0</v>
       </c>
@@ -12185,19 +12129,19 @@
       <c r="C20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f>'参数设置'!E7</f>
         <v>0.08</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <f>'参数设置'!C23</f>
         <v>-0.22</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="9">
         <f>D20*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="9">
         <f>E20*F20</f>
         <v>-176000.0</v>
       </c>
@@ -12212,19 +12156,19 @@
       <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f>'参数设置'!E8</f>
         <v>0.09</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="10">
         <f>'参数设置'!C24</f>
         <v>-0.1</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="9">
         <f>D21*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="9">
         <f>E21*F21</f>
         <v>-90000.0</v>
       </c>
@@ -12239,19 +12183,19 @@
       <c r="C22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f>'参数设置'!E9</f>
         <v>0.07</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <f>'参数设置'!C24</f>
         <v>-0.1</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="9">
         <f>D22*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="9">
         <f>E22*F22</f>
         <v>-70000.00000000001</v>
       </c>
@@ -12266,19 +12210,19 @@
       <c r="C23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f>'参数设置'!E10</f>
         <v>0.09</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="10">
         <f>'参数设置'!C25</f>
         <v>-0.14</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="9">
         <f>D23*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="9">
         <f>E23*F23</f>
         <v>-126000.00000000001</v>
       </c>
@@ -12293,19 +12237,19 @@
       <c r="C24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f>'参数设置'!E11</f>
         <v>0.08</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="10">
         <f>'参数设置'!C25</f>
         <v>-0.14</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="9">
         <f>D24*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="9">
         <f>E24*F24</f>
         <v>-112000.00000000001</v>
       </c>
@@ -12320,19 +12264,19 @@
       <c r="C25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <f>'参数设置'!E12</f>
         <v>0.08</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="10">
         <f>'参数设置'!C26</f>
         <v>-0.17</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="9">
         <f>D25*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="9">
         <f>E25*F25</f>
         <v>-136000.0</v>
       </c>
@@ -12347,19 +12291,19 @@
       <c r="C26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <f>'参数设置'!E13</f>
         <v>0.07</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <f>'参数设置'!C26</f>
         <v>-0.17</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="9">
         <f>D26*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="9">
         <f>E26*F26</f>
         <v>-119000.00000000003</v>
       </c>
@@ -12374,19 +12318,19 @@
       <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <f>'参数设置'!E14</f>
         <v>0.08</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <f>'参数设置'!C27</f>
         <v>-0.19</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="9">
         <f>D27*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="9">
         <f>E27*F27</f>
         <v>-152000.0</v>
       </c>
@@ -12401,19 +12345,19 @@
       <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <f>'参数设置'!E15</f>
         <v>0.07</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="10">
         <f>'参数设置'!C27</f>
         <v>-0.19</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="9">
         <f>D28*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="9">
         <f>E28*F28</f>
         <v>-133000.00000000003</v>
       </c>
@@ -12428,19 +12372,19 @@
       <c r="C29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <f>'参数设置'!E4</f>
         <v>0.1</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="10">
         <f>'参数设置'!D22</f>
         <v>0.16</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="9">
         <f>D29*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="9">
         <f>E29*F29</f>
         <v>160000.0</v>
       </c>
@@ -12455,19 +12399,19 @@
       <c r="C30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <f>'参数设置'!E5</f>
         <v>0.09</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="10">
         <f>'参数设置'!D22</f>
         <v>0.16</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="9">
         <f>D30*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="9">
         <f>E30*F30</f>
         <v>144000.0</v>
       </c>
@@ -12482,19 +12426,19 @@
       <c r="C31" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <f>'参数设置'!E6</f>
         <v>0.1</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="10">
         <f>'参数设置'!D23</f>
         <v>0.07</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="9">
         <f>D31*'参数设置'!$B$3</f>
         <v>1000000.0</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="9">
         <f>E31*F31</f>
         <v>70000.0</v>
       </c>
@@ -12509,19 +12453,19 @@
       <c r="C32" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <f>'参数设置'!E7</f>
         <v>0.08</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="10">
         <f>'参数设置'!D23</f>
         <v>0.07</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="9">
         <f>D32*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="9">
         <f>E32*F32</f>
         <v>56000.00000000001</v>
       </c>
@@ -12536,19 +12480,19 @@
       <c r="C33" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <f>'参数设置'!E8</f>
         <v>0.09</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="10">
         <f>'参数设置'!D24</f>
         <v>0.09</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="9">
         <f>D33*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="9">
         <f>E33*F33</f>
         <v>81000.0</v>
       </c>
@@ -12563,19 +12507,19 @@
       <c r="C34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <f>'参数设置'!E9</f>
         <v>0.07</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <f>'参数设置'!D24</f>
         <v>0.09</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="9">
         <f>D34*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="9">
         <f>E34*F34</f>
         <v>63000.00000000001</v>
       </c>
@@ -12590,19 +12534,19 @@
       <c r="C35" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <f>'参数设置'!E10</f>
         <v>0.09</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="10">
         <f>'参数设置'!D25</f>
         <v>0.11</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="9">
         <f>D35*'参数设置'!$B$3</f>
         <v>900000.0</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="9">
         <f>E35*F35</f>
         <v>99000.0</v>
       </c>
@@ -12617,19 +12561,19 @@
       <c r="C36" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <f>'参数设置'!E11</f>
         <v>0.08</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="10">
         <f>'参数设置'!D25</f>
         <v>0.11</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="9">
         <f>D36*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="9">
         <f>E36*F36</f>
         <v>88000.0</v>
       </c>
@@ -12644,19 +12588,19 @@
       <c r="C37" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <f>'参数设置'!E12</f>
         <v>0.08</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="10">
         <f>'参数设置'!D26</f>
         <v>0.05</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="9">
         <f>D37*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="9">
         <f>E37*F37</f>
         <v>40000.0</v>
       </c>
@@ -12671,19 +12615,19 @@
       <c r="C38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <f>'参数设置'!E13</f>
         <v>0.07</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="10">
         <f>'参数设置'!D26</f>
         <v>0.05</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="9">
         <f>D38*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="9">
         <f>E38*F38</f>
         <v>35000.00000000001</v>
       </c>
@@ -12698,19 +12642,19 @@
       <c r="C39" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <f>'参数设置'!E14</f>
         <v>0.08</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="10">
         <f>'参数设置'!D27</f>
         <v>0.1</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="9">
         <f>D39*'参数设置'!$B$3</f>
         <v>800000.0</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="9">
         <f>E39*F39</f>
         <v>80000.0</v>
       </c>
@@ -12725,19 +12669,19 @@
       <c r="C40" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <f>'参数设置'!E15</f>
         <v>0.07</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="10">
         <f>'参数设置'!D27</f>
         <v>0.1</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="9">
         <f>D40*'参数设置'!$B$3</f>
         <v>700000.0000000001</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="9">
         <f>E40*F40</f>
         <v>70000.00000000001</v>
       </c>
@@ -12811,36 +12755,36 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="15">
+      <c r="A4" s="11">
         <f>'组合分析'!B22</f>
         <v>0.13062683565537636</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="D4" s="15">
+      <c r="B4" s="11"/>
+      <c r="D4" s="11">
         <f>'组合分析'!B23</f>
         <v>0.11455607034702364</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="G4" s="15">
+      <c r="E4" s="11"/>
+      <c r="G4" s="11">
         <f>'组合分析'!B25/'参数设置'!B3</f>
         <v>0.05439930944790144</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="J4" s="15">
+      <c r="H4" s="11"/>
+      <c r="J4" s="11">
         <f>'组合分析'!B27</f>
         <v>-0.1293314203092506</v>
       </c>
-      <c r="K4" s="15"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="7" t="s">
@@ -12868,19 +12812,19 @@
       <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="14" t="str">
+      <c r="B9" s="4" t="str">
         <f>'组合分析'!A6</f>
         <v>S001</v>
       </c>
-      <c r="C9" s="16" t="str">
+      <c r="C9" s="5" t="str">
         <f>'组合分析'!B6</f>
         <v>华曜科技</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f>'组合分析'!M6</f>
         <v>0.1</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="9">
         <f>'组合分析'!P6</f>
         <v>69186.57022522126</v>
       </c>
@@ -12889,19 +12833,19 @@
       <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="14" t="str">
+      <c r="B10" s="4" t="str">
         <f>'组合分析'!A10</f>
         <v>S005</v>
       </c>
-      <c r="C10" s="16" t="str">
+      <c r="C10" s="5" t="str">
         <f>'组合分析'!B10</f>
         <v>远岭医药</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f>'组合分析'!M10</f>
         <v>0.09</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="9">
         <f>'组合分析'!P10</f>
         <v>65111.89330989353</v>
       </c>
@@ -12910,19 +12854,19 @@
       <c r="A11" s="4">
         <v>3</v>
       </c>
-      <c r="B11" s="14" t="str">
+      <c r="B11" s="4" t="str">
         <f>'组合分析'!A8</f>
         <v>S003</v>
       </c>
-      <c r="C11" s="16" t="str">
+      <c r="C11" s="5" t="str">
         <f>'组合分析'!B8</f>
         <v>江海银行</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f>'组合分析'!M8</f>
         <v>0.1</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="9">
         <f>'组合分析'!P8</f>
         <v>63964.67780913862</v>
       </c>
@@ -12931,19 +12875,19 @@
       <c r="A12" s="4">
         <v>4</v>
       </c>
-      <c r="B12" s="14" t="str">
+      <c r="B12" s="4" t="str">
         <f>'组合分析'!A9</f>
         <v>S004</v>
       </c>
-      <c r="C12" s="16" t="str">
+      <c r="C12" s="5" t="str">
         <f>'组合分析'!B9</f>
         <v>安信证券</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>'组合分析'!M9</f>
         <v>0.08</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="9">
         <f>'组合分析'!P9</f>
         <v>55817.83048664134</v>
       </c>
@@ -12952,19 +12896,19 @@
       <c r="A13" s="4">
         <v>5</v>
       </c>
-      <c r="B13" s="14" t="str">
+      <c r="B13" s="4" t="str">
         <f>'组合分析'!A17</f>
         <v>S012</v>
       </c>
-      <c r="C13" s="16" t="str">
+      <c r="C13" s="5" t="str">
         <f>'组合分析'!B17</f>
         <v>锐虎机械</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f>'组合分析'!M17</f>
         <v>0.07</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="9">
         <f>'组合分析'!P17</f>
         <v>54267.000379465695</v>
       </c>
@@ -13041,31 +12985,31 @@
       <c r="A4" s="3">
         <v>45351</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <f>('月度收益'!B2*'参数设置'!E4+'月度收益'!C2*'参数设置'!E5)/B$30</f>
         <v>0.040139355480900946</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <f>('月度收益'!D2*'参数设置'!E6+'月度收益'!E2*'参数设置'!E7)/C$30</f>
         <v>0.020651090272624392</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <f>('月度收益'!F2*'参数设置'!E8+'月度收益'!G2*'参数设置'!E9)/D$30</f>
         <v>0.013669662309368169</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <f>('月度收益'!H2*'参数设置'!E10+'月度收益'!I2*'参数设置'!E11)/E$30</f>
         <v>0.03647807528967561</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <f>('月度收益'!J2*'参数设置'!E12+'月度收益'!K2*'参数设置'!E13)/F$30</f>
         <v>0.06701066762555423</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f>('月度收益'!L2*'参数设置'!E14+'月度收益'!M2*'参数设置'!E15)/G$30</f>
         <v>0.04900423033756366</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <f>SUMPRODUCT(B4:G4,$B$30:$G$30)</f>
         <v>0.037134327253655015</v>
       </c>
@@ -13074,31 +13018,31 @@
       <c r="A5" s="3">
         <v>45382</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <f>('月度收益'!B3*'参数设置'!E4+'月度收益'!C3*'参数设置'!E5)/B$30</f>
         <v>0.02080385405767845</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <f>('月度收益'!D3*'参数设置'!E6+'月度收益'!E3*'参数设置'!E7)/C$30</f>
         <v>0.0037386422908783543</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>('月度收益'!F3*'参数设置'!E8+'月度收益'!G3*'参数设置'!E9)/D$30</f>
         <v>0.05583968262556071</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <f>('月度收益'!H3*'参数设置'!E10+'月度收益'!I3*'参数设置'!E11)/E$30</f>
         <v>0.03811238569504865</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f>('月度收益'!J3*'参数设置'!E12+'月度收益'!K3*'参数设置'!E13)/F$30</f>
         <v>0.020420169855812038</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <f>('月度收益'!L3*'参数设置'!E14+'月度收益'!M3*'参数设置'!E15)/G$30</f>
         <v>0.05542962370730448</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <f>SUMPRODUCT(B5:G5,$B$30:$G$30)</f>
         <v>0.03141661170603247</v>
       </c>
@@ -13107,31 +13051,31 @@
       <c r="A6" s="3">
         <v>45412</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <f>('月度收益'!B4*'参数设置'!E4+'月度收益'!C4*'参数设置'!E5)/B$30</f>
         <v>-0.007228174446060708</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <f>('月度收益'!D4*'参数设置'!E6+'月度收益'!E4*'参数设置'!E7)/C$30</f>
         <v>0.020629579656771063</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>('月度收益'!F4*'参数设置'!E8+'月度收益'!G4*'参数设置'!E9)/D$30</f>
         <v>0.02581346795889433</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <f>('月度收益'!H4*'参数设置'!E10+'月度收益'!I4*'参数设置'!E11)/E$30</f>
         <v>0.025526481616359155</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>('月度收益'!J4*'参数设置'!E12+'月度收益'!K4*'参数设置'!E13)/F$30</f>
         <v>0.02233543415289657</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f>('月度收益'!L4*'参数设置'!E14+'月度收益'!M4*'参数设置'!E15)/G$30</f>
         <v>0.005161521797419184</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <f>SUMPRODUCT(B6:G6,$B$30:$G$30)</f>
         <v>0.01493417133421877</v>
       </c>
@@ -13140,31 +13084,31 @@
       <c r="A7" s="3">
         <v>45443</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <f>('月度收益'!B5*'参数设置'!E4+'月度收益'!C5*'参数设置'!E5)/B$30</f>
         <v>-0.02222776901172087</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <f>('月度收益'!D5*'参数设置'!E6+'月度收益'!E5*'参数设置'!E7)/C$30</f>
         <v>0.020250046185193944</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>('月度收益'!F5*'参数设置'!E8+'月度收益'!G5*'参数设置'!E9)/D$30</f>
         <v>0.000567315205726478</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <f>('月度收益'!H5*'参数设置'!E10+'月度收益'!I5*'参数设置'!E11)/E$30</f>
         <v>0.011665971786331273</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f>('月度收益'!J5*'参数设置'!E12+'月度收益'!K5*'参数设置'!E13)/F$30</f>
         <v>0.003185561184784873</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f>('月度收益'!L5*'参数设置'!E14+'月度收益'!M5*'参数设置'!E15)/G$30</f>
         <v>-0.022825104955650183</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <f>SUMPRODUCT(B7:G7,$B$30:$G$30)</f>
         <v>-0.0014502137279292998</v>
       </c>
@@ -13173,31 +13117,31 @@
       <c r="A8" s="3">
         <v>45473</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <f>('月度收益'!B6*'参数设置'!E4+'月度收益'!C6*'参数设置'!E5)/B$30</f>
         <v>-0.011313775442622954</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f>('月度收益'!D6*'参数设置'!E6+'月度收益'!E6*'参数设置'!E7)/C$30</f>
         <v>0.003550405774603811</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f>('月度收益'!F6*'参数设置'!E8+'月度收益'!G6*'参数设置'!E9)/D$30</f>
         <v>0.016403385046832347</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <f>('月度收益'!H6*'参数设置'!E10+'月度收益'!I6*'参数设置'!E11)/E$30</f>
         <v>0.0021509669202346244</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>('月度收益'!J6*'参数设置'!E12+'月度收益'!K6*'参数设置'!E13)/F$30</f>
         <v>-0.023032810294347783</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <f>('月度收益'!L6*'参数设置'!E14+'月度收益'!M6*'参数设置'!E15)/G$30</f>
         <v>-0.007750425507905723</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <f>SUMPRODUCT(B8:G8,$B$30:$G$30)</f>
         <v>-0.00313782368107464</v>
       </c>
@@ -13206,31 +13150,31 @@
       <c r="A9" s="3">
         <v>45504</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <f>('月度收益'!B7*'参数设置'!E4+'月度收益'!C7*'参数设置'!E5)/B$30</f>
         <v>0.0035811667496765546</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f>('月度收益'!D7*'参数设置'!E6+'月度收益'!E7*'参数设置'!E7)/C$30</f>
         <v>0.005457952826373908</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f>('月度收益'!F7*'参数设置'!E8+'月度收益'!G7*'参数设置'!E9)/D$30</f>
         <v>0.0008187515588026138</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <f>('月度收益'!H7*'参数设置'!E10+'月度收益'!I7*'参数设置'!E11)/E$30</f>
         <v>-0.000374805292396758</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f>('月度收益'!J7*'参数设置'!E12+'月度收益'!K7*'参数设置'!E13)/F$30</f>
         <v>-0.00584057752938653</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <f>('月度收益'!L7*'参数设置'!E14+'月度收益'!M7*'参数设置'!E15)/G$30</f>
         <v>-0.0024049367868581866</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <f>SUMPRODUCT(B9:G9,$B$30:$G$30)</f>
         <v>0.0004933093934501105</v>
       </c>
@@ -13239,31 +13183,31 @@
       <c r="A10" s="3">
         <v>45535</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <f>('月度收益'!B8*'参数设置'!E4+'月度收益'!C8*'参数设置'!E5)/B$30</f>
         <v>-0.020235298066595075</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <f>('月度收益'!D8*'参数设置'!E6+'月度收益'!E8*'参数设置'!E7)/C$30</f>
         <v>-0.027467300822028813</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f>('月度收益'!F8*'参数设置'!E8+'月度收益'!G8*'参数设置'!E9)/D$30</f>
         <v>-0.05035420244779837</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <f>('月度收益'!H8*'参数设置'!E10+'月度收益'!I8*'参数设置'!E11)/E$30</f>
         <v>-0.038232126407437325</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f>('月度收益'!J8*'参数设置'!E12+'月度收益'!K8*'参数设置'!E13)/F$30</f>
         <v>-0.05376381852977597</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <f>('月度收益'!L8*'参数设置'!E14+'月度收益'!M8*'参数设置'!E15)/G$30</f>
         <v>-0.05289302647028515</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f>SUMPRODUCT(B10:G10,$B$30:$G$30)</f>
         <v>-0.0393434814115395</v>
       </c>
@@ -13272,31 +13216,31 @@
       <c r="A11" s="3">
         <v>45565</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <f>('月度收益'!B9*'参数设置'!E4+'月度收益'!C9*'参数设置'!E5)/B$30</f>
         <v>0.035076533423352575</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f>('月度收益'!D9*'参数设置'!E6+'月度收益'!E9*'参数设置'!E7)/C$30</f>
         <v>0.04268829926866749</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f>('月度收益'!F9*'参数设置'!E8+'月度收益'!G9*'参数设置'!E9)/D$30</f>
         <v>0.03726166890218514</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f>('月度收益'!H9*'参数设置'!E10+'月度收益'!I9*'参数设置'!E11)/E$30</f>
         <v>0.017740523144794126</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f>('月度收益'!J9*'参数设置'!E12+'月度收益'!K9*'参数设置'!E13)/F$30</f>
         <v>0.027252080025214818</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <f>('月度收益'!L9*'参数设置'!E14+'月度收益'!M9*'参数设置'!E15)/G$30</f>
         <v>0.04852557393530639</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <f>SUMPRODUCT(B11:G11,$B$30:$G$30)</f>
         <v>0.03469283927183994</v>
       </c>
@@ -13305,31 +13249,31 @@
       <c r="A12" s="3">
         <v>45596</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <f>('月度收益'!B10*'参数设置'!E4+'月度收益'!C10*'参数设置'!E5)/B$30</f>
         <v>0.040978993500349926</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f>('月度收益'!D10*'参数设置'!E6+'月度收益'!E10*'参数设置'!E7)/C$30</f>
         <v>0.05026293846780755</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f>('月度收益'!F10*'参数设置'!E8+'月度收益'!G10*'参数设置'!E9)/D$30</f>
         <v>0.042615542161327014</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f>('月度收益'!H10*'参数设置'!E10+'月度收益'!I10*'参数设置'!E11)/E$30</f>
         <v>0.020087850161690027</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f>('月度收益'!J10*'参数设置'!E12+'月度收益'!K10*'参数设置'!E13)/F$30</f>
         <v>0.029835922086186094</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f>('月度收益'!L10*'参数设置'!E14+'月度收益'!M10*'参数设置'!E15)/G$30</f>
         <v>0.054170471693309956</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <f>SUMPRODUCT(B12:G12,$B$30:$G$30)</f>
         <v>0.03966771802949588</v>
       </c>
@@ -13338,31 +13282,31 @@
       <c r="A13" s="3">
         <v>45626</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <f>('月度收益'!B11*'参数设置'!E4+'月度收益'!C11*'参数设置'!E5)/B$30</f>
         <v>0.07417460712986</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f>('月度收益'!D11*'参数设置'!E6+'月度收益'!E11*'参数设置'!E7)/C$30</f>
         <v>0.07684454053421894</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f>('月度收益'!F11*'参数设置'!E8+'月度收益'!G11*'参数设置'!E9)/D$30</f>
         <v>0.06876859155135966</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <f>('月度收益'!H11*'参数设置'!E10+'月度收益'!I11*'参数设置'!E11)/E$30</f>
         <v>0.05489245746139359</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f>('月度收益'!J11*'参数设置'!E12+'月度收益'!K11*'参数设置'!E13)/F$30</f>
         <v>0.08943395692237263</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <f>('月度收益'!L11*'参数设置'!E14+'月度收益'!M11*'参数设置'!E15)/G$30</f>
         <v>0.09825934733782535</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <f>SUMPRODUCT(B13:G13,$B$30:$G$30)</f>
         <v>0.07641388070651696</v>
       </c>
@@ -13371,31 +13315,31 @@
       <c r="A14" s="3">
         <v>45657</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <f>('月度收益'!B12*'参数设置'!E4+'月度收益'!C12*'参数设置'!E5)/B$30</f>
         <v>0.023740886310502723</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f>('月度收益'!D12*'参数设置'!E6+'月度收益'!E12*'参数设置'!E7)/C$30</f>
         <v>-0.01330216567710517</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f>('月度收益'!F12*'参数设置'!E8+'月度收益'!G12*'参数设置'!E9)/D$30</f>
         <v>0.008272708246466335</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <f>('月度收益'!H12*'参数设置'!E10+'月度收益'!I12*'参数设置'!E11)/E$30</f>
         <v>0.005541047316630305</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f>('月度收益'!J12*'参数设置'!E12+'月度收益'!K12*'参数设置'!E13)/F$30</f>
         <v>0.010798258529030401</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <f>('月度收益'!L12*'参数设置'!E14+'月度收益'!M12*'参数设置'!E15)/G$30</f>
         <v>0.03427390594401737</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <f>SUMPRODUCT(B14:G14,$B$30:$G$30)</f>
         <v>0.011142814611335518</v>
       </c>
@@ -13404,31 +13348,31 @@
       <c r="A15" s="3">
         <v>45688</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <f>('月度收益'!B13*'参数设置'!E4+'月度收益'!C13*'参数设置'!E5)/B$30</f>
         <v>-0.006358610105040377</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f>('月度收益'!D13*'参数设置'!E6+'月度收益'!E13*'参数设置'!E7)/C$30</f>
         <v>-0.02906886030973625</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f>('月度收益'!F13*'参数设置'!E8+'月度收益'!G13*'参数设置'!E9)/D$30</f>
         <v>-0.026680696386815275</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <f>('月度收益'!H13*'参数设置'!E10+'月度收益'!I13*'参数设置'!E11)/E$30</f>
         <v>-0.002696891820455242</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f>('月度收益'!J13*'参数设置'!E12+'月度收益'!K13*'参数设置'!E13)/F$30</f>
         <v>-0.009549276010915663</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <f>('月度收益'!L13*'参数设置'!E14+'月度收益'!M13*'参数设置'!E15)/G$30</f>
         <v>-0.0017735587325099433</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <f>SUMPRODUCT(B15:G15,$B$30:$G$30)</f>
         <v>-0.012866339018591872</v>
       </c>
@@ -13437,31 +13381,31 @@
       <c r="A16" s="3">
         <v>45716</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <f>('月度收益'!B14*'参数设置'!E4+'月度收益'!C14*'参数设置'!E5)/B$30</f>
         <v>-0.03863404738835578</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f>('月度收益'!D14*'参数设置'!E6+'月度收益'!E14*'参数设置'!E7)/C$30</f>
         <v>-0.016104269351907008</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f>('月度收益'!F14*'参数设置'!E8+'月度收益'!G14*'参数设置'!E9)/D$30</f>
         <v>-0.053606696034521194</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <f>('月度收益'!H14*'参数设置'!E10+'月度收益'!I14*'参数设置'!E11)/E$30</f>
         <v>-0.011369876408700267</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f>('月度收益'!J14*'参数设置'!E12+'月度收益'!K14*'参数设置'!E13)/F$30</f>
         <v>9.217557256466685e-05</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <f>('月度收益'!L14*'参数设置'!E14+'月度收益'!M14*'参数设置'!E15)/G$30</f>
         <v>-0.05229502306702795</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="10">
         <f>SUMPRODUCT(B16:G16,$B$30:$G$30)</f>
         <v>-0.02857961496630279</v>
       </c>
@@ -13470,31 +13414,31 @@
       <c r="A17" s="3">
         <v>45747</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <f>('月度收益'!B15*'参数设置'!E4+'月度收益'!C15*'参数设置'!E5)/B$30</f>
         <v>-0.05256735401347983</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <f>('月度收益'!D15*'参数设置'!E6+'月度收益'!E15*'参数设置'!E7)/C$30</f>
         <v>-0.027196286681917762</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f>('月度收益'!F15*'参数设置'!E8+'月度收益'!G15*'参数设置'!E9)/D$30</f>
         <v>-0.003974310292359284</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <f>('月度收益'!H15*'参数设置'!E10+'月度收益'!I15*'参数设置'!E11)/E$30</f>
         <v>-0.002688052052589701</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f>('月度收益'!J15*'参数设置'!E12+'月度收益'!K15*'参数设置'!E13)/F$30</f>
         <v>-0.04087339470080129</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <f>('月度收益'!L15*'参数设置'!E14+'月度收益'!M15*'参数设置'!E15)/G$30</f>
         <v>-0.04044612763906296</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <f>SUMPRODUCT(B17:G17,$B$30:$G$30)</f>
         <v>-0.02817391571200374</v>
       </c>
@@ -13503,31 +13447,31 @@
       <c r="A18" s="3">
         <v>45777</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <f>('月度收益'!B16*'参数设置'!E4+'月度收益'!C16*'参数设置'!E5)/B$30</f>
         <v>-0.07682077646964937</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <f>('月度收益'!D16*'参数设置'!E6+'月度收益'!E16*'参数设置'!E7)/C$30</f>
         <v>-0.08592127906989991</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f>('月度收益'!F16*'参数设置'!E8+'月度收益'!G16*'参数设置'!E9)/D$30</f>
         <v>-0.08592368636514157</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <f>('月度收益'!H16*'参数设置'!E10+'月度收益'!I16*'参数设置'!E11)/E$30</f>
         <v>-0.03519232117674543</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f>('月度收益'!J16*'参数设置'!E12+'月度收益'!K16*'参数设置'!E13)/F$30</f>
         <v>-0.045792742392673454</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <f>('月度收益'!L16*'参数设置'!E14+'月度收益'!M16*'参数设置'!E15)/G$30</f>
         <v>-0.06033345819768108</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="10">
         <f>SUMPRODUCT(B18:G18,$B$30:$G$30)</f>
         <v>-0.06571119226883793</v>
       </c>
@@ -13536,31 +13480,31 @@
       <c r="A19" s="3">
         <v>45808</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <f>('月度收益'!B17*'参数设置'!E4+'月度收益'!C17*'参数设置'!E5)/B$30</f>
         <v>0.007422258564939768</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <f>('月度收益'!D17*'参数设置'!E6+'月度收益'!E17*'参数设置'!E7)/C$30</f>
         <v>0.025005074323266256</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f>('月度收益'!F17*'参数设置'!E8+'月度收益'!G17*'参数设置'!E9)/D$30</f>
         <v>0.033664573556926466</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <f>('月度收益'!H17*'参数设置'!E10+'月度收益'!I17*'参数设置'!E11)/E$30</f>
         <v>0.0249709674086924</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <f>('月度收益'!J17*'参数设置'!E12+'月度收益'!K17*'参数设置'!E13)/F$30</f>
         <v>0.014827501431142752</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="10">
         <f>('月度收益'!L17*'参数设置'!E14+'月度收益'!M17*'参数设置'!E15)/G$30</f>
         <v>0.014285827311424238</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="10">
         <f>SUMPRODUCT(B19:G19,$B$30:$G$30)</f>
         <v>0.01990953804549747</v>
       </c>
@@ -13569,31 +13513,31 @@
       <c r="A20" s="3">
         <v>45838</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <f>('月度收益'!B18*'参数设置'!E4+'月度收益'!C18*'参数设置'!E5)/B$30</f>
         <v>0.04966302038604869</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="10">
         <f>('月度收益'!D18*'参数设置'!E6+'月度收益'!E18*'参数设置'!E7)/C$30</f>
         <v>0.0746369663227838</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f>('月度收益'!F18*'参数设置'!E8+'月度收益'!G18*'参数设置'!E9)/D$30</f>
         <v>0.07301274056228317</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <f>('月度收益'!H18*'参数设置'!E10+'月度收益'!I18*'参数设置'!E11)/E$30</f>
         <v>0.033339848957377724</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <f>('月度收益'!J18*'参数设置'!E12+'月度收益'!K18*'参数设置'!E13)/F$30</f>
         <v>0.011533113777284512</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <f>('月度收益'!L18*'参数设置'!E14+'月度收益'!M18*'参数设置'!E15)/G$30</f>
         <v>0.013317023917036491</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="10">
         <f>SUMPRODUCT(B20:G20,$B$30:$G$30)</f>
         <v>0.043947961278318</v>
       </c>
@@ -13602,31 +13546,31 @@
       <c r="A21" s="3">
         <v>45869</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <f>('月度收益'!B19*'参数设置'!E4+'月度收益'!C19*'参数设置'!E5)/B$30</f>
         <v>0.055984617823067406</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <f>('月度收益'!D19*'参数设置'!E6+'月度收益'!E19*'参数设置'!E7)/C$30</f>
         <v>0.046818233947262804</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f>('月度收益'!F19*'参数设置'!E8+'月度收益'!G19*'参数设置'!E9)/D$30</f>
         <v>0.028919127733900003</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="10">
         <f>('月度收益'!H19*'参数设置'!E10+'月度收益'!I19*'参数设置'!E11)/E$30</f>
         <v>0.02765961374325402</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <f>('月度收益'!J19*'参数设置'!E12+'月度收益'!K19*'参数设置'!E13)/F$30</f>
         <v>0.04883532205717295</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="10">
         <f>('月度收益'!L19*'参数设置'!E14+'月度收益'!M19*'参数设置'!E15)/G$30</f>
         <v>0.043670417025752827</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="10">
         <f>SUMPRODUCT(B21:G21,$B$30:$G$30)</f>
         <v>0.04226941513310616</v>
       </c>
@@ -13635,31 +13579,31 @@
       <c r="A22" s="3">
         <v>45900</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <f>('月度收益'!B20*'参数设置'!E4+'月度收益'!C20*'参数设置'!E5)/B$30</f>
         <v>0.03685172961810691</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <f>('月度收益'!D20*'参数设置'!E6+'月度收益'!E20*'参数设置'!E7)/C$30</f>
         <v>0.017531689709682517</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f>('月度收益'!F20*'参数设置'!E8+'月度收益'!G20*'参数设置'!E9)/D$30</f>
         <v>0.04836283771322886</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <f>('月度收益'!H20*'参数设置'!E10+'月度收益'!I20*'参数设置'!E11)/E$30</f>
         <v>0.012257314223147192</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <f>('月度收益'!J20*'参数设置'!E12+'月度收益'!K20*'参数设置'!E13)/F$30</f>
         <v>-0.0017643462245952094</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="10">
         <f>('月度收益'!L20*'参数设置'!E14+'月度收益'!M20*'参数设置'!E15)/G$30</f>
         <v>0.05262318284817849</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="10">
         <f>SUMPRODUCT(B22:G22,$B$30:$G$30)</f>
         <v>0.0276081557207723</v>
       </c>
@@ -13668,31 +13612,31 @@
       <c r="A23" s="3">
         <v>45930</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <f>('月度收益'!B21*'参数设置'!E4+'月度收益'!C21*'参数设置'!E5)/B$30</f>
         <v>0.043403371148473494</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <f>('月度收益'!D21*'参数设置'!E6+'月度收益'!E21*'参数设置'!E7)/C$30</f>
         <v>0.06778992126884449</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f>('月度收益'!F21*'参数设置'!E8+'月度收益'!G21*'参数设置'!E9)/D$30</f>
         <v>0.057589890249146805</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="10">
         <f>('月度收益'!H21*'参数设置'!E10+'月度收益'!I21*'参数设置'!E11)/E$30</f>
         <v>0.03230804044638717</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="10">
         <f>('月度收益'!J21*'参数设置'!E12+'月度收益'!K21*'参数设置'!E13)/F$30</f>
         <v>0.04924500137719234</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="10">
         <f>('月度收益'!L21*'参数设置'!E14+'月度收益'!M21*'参数设置'!E15)/G$30</f>
         <v>0.06633428368329597</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="10">
         <f>SUMPRODUCT(B23:G23,$B$30:$G$30)</f>
         <v>0.05249246842142453</v>
       </c>
@@ -13701,31 +13645,31 @@
       <c r="A24" s="3">
         <v>45961</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <f>('月度收益'!B22*'参数设置'!E4+'月度收益'!C22*'参数设置'!E5)/B$30</f>
         <v>-0.007607175861628576</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="10">
         <f>('月度收益'!D22*'参数设置'!E6+'月度收益'!E22*'参数设置'!E7)/C$30</f>
         <v>0.012537961788336573</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f>('月度收益'!F22*'参数设置'!E8+'月度收益'!G22*'参数设置'!E9)/D$30</f>
         <v>-0.02622343721893637</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="10">
         <f>('月度收益'!H22*'参数设置'!E10+'月度收益'!I22*'参数设置'!E11)/E$30</f>
         <v>-0.011514689819452984</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <f>('月度收益'!J22*'参数设置'!E12+'月度收益'!K22*'参数设置'!E13)/F$30</f>
         <v>0.0016114089987813323</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="10">
         <f>('月度收益'!L22*'参数设置'!E14+'月度收益'!M22*'参数设置'!E15)/G$30</f>
         <v>-0.009081894459468838</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="10">
         <f>SUMPRODUCT(B24:G24,$B$30:$G$30)</f>
         <v>-0.006462350335248799</v>
       </c>
@@ -13734,31 +13678,31 @@
       <c r="A25" s="3">
         <v>45991</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <f>('月度收益'!B23*'参数设置'!E4+'月度收益'!C23*'参数设置'!E5)/B$30</f>
         <v>-0.004764339144909995</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <f>('月度收益'!D23*'参数设置'!E6+'月度收益'!E23*'参数设置'!E7)/C$30</f>
         <v>-0.011889120173846074</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <f>('月度收益'!F23*'参数设置'!E8+'月度收益'!G23*'参数设置'!E9)/D$30</f>
         <v>-0.007722565476647021</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="10">
         <f>('月度收益'!H23*'参数设置'!E10+'月度收益'!I23*'参数设置'!E11)/E$30</f>
         <v>-0.0080552459482691</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="10">
         <f>('月度收益'!J23*'参数设置'!E12+'月度收益'!K23*'参数设置'!E13)/F$30</f>
         <v>-0.011049918225097738</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="10">
         <f>('月度收益'!L23*'参数设置'!E14+'月度收益'!M23*'参数设置'!E15)/G$30</f>
         <v>0.012447226669546785</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="10">
         <f>SUMPRODUCT(B25:G25,$B$30:$G$30)</f>
         <v>-0.005440672089627106</v>
       </c>
@@ -13767,31 +13711,31 @@
       <c r="A26" s="3">
         <v>46022</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <f>('月度收益'!B24*'参数设置'!E4+'月度收益'!C24*'参数设置'!E5)/B$30</f>
         <v>0.007250300375761576</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="10">
         <f>('月度收益'!D24*'参数设置'!E6+'月度收益'!E24*'参数设置'!E7)/C$30</f>
         <v>-0.0070612090100724435</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <f>('月度收益'!F24*'参数设置'!E8+'月度收益'!G24*'参数设置'!E9)/D$30</f>
         <v>-0.007837598081442632</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <f>('月度收益'!H24*'参数设置'!E10+'月度收益'!I24*'参数设置'!E11)/E$30</f>
         <v>0.008372710552405287</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="10">
         <f>('月度收益'!J24*'参数设置'!E12+'月度收益'!K24*'参数设置'!E13)/F$30</f>
         <v>0.023113258861488004</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="10">
         <f>('月度收益'!L24*'参数设置'!E14+'月度收益'!M24*'参数设置'!E15)/G$30</f>
         <v>0.02540872660799677</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="10">
         <f>SUMPRODUCT(B26:G26,$B$30:$G$30)</f>
         <v>0.007554182370882454</v>
       </c>
@@ -13823,27 +13767,27 @@
       <c r="A30" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <f>SUM('参数设置'!E4:E5)</f>
         <v>0.19</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="10">
         <f>SUM('参数设置'!E6:E7)</f>
         <v>0.18</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <f>SUM('参数设置'!E8:E9)</f>
         <v>0.16</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="10">
         <f>SUM('参数设置'!E10:E11)</f>
         <v>0.16999999999999998</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="10">
         <f>SUM('参数设置'!E12:E13)</f>
         <v>0.15000000000000002</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="10">
         <f>SUM('参数设置'!E14:E15)</f>
         <v>0.15000000000000002</v>
       </c>
@@ -13887,43 +13831,43 @@
       <c r="A33" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="6">
         <f>COVARIANCE.S(B$4:B$26,B$4:B$26)</f>
         <v>0.0013524084576669244</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="6">
         <f>COVARIANCE.S(B$4:B$26,C$4:C$26)</f>
         <v>0.001199265661419234</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="6">
         <f>COVARIANCE.S(B$4:B$26,D$4:D$26)</f>
         <v>0.001255970611206699</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="6">
         <f>COVARIANCE.S(B$4:B$26,E$4:E$26)</f>
         <v>0.000678949334674663</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="6">
         <f>COVARIANCE.S(B$4:B$26,F$4:F$26)</f>
         <v>0.0010365458850546678</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="6">
         <f>COVARIANCE.S(B$4:B$26,G$4:G$26)</f>
         <v>0.0014133312018288144</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="6">
         <f>SUMPRODUCT(B33:G33,$B$30:$G$30)</f>
         <v>0.0011566836737324647</v>
       </c>
-      <c r="I33" s="13">
+      <c r="I33" s="9">
         <f>B$30*H33*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>109321.76240762952</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="9">
         <f>I33/B$30</f>
         <v>575377.6968822606</v>
       </c>
-      <c r="K33" s="13">
+      <c r="K33" s="9">
         <f>B$30*STDEV.S(B$4:B$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>114940.59534792692</v>
       </c>
@@ -13932,43 +13876,43 @@
       <c r="A34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="6">
         <f>COVARIANCE.S(C$4:C$26,B$4:B$26)</f>
         <v>0.001199265661419234</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="6">
         <f>COVARIANCE.S(C$4:C$26,C$4:C$26)</f>
         <v>0.0014632106602867462</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="6">
         <f>COVARIANCE.S(C$4:C$26,D$4:D$26)</f>
         <v>0.0013546728920645023</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="6">
         <f>COVARIANCE.S(C$4:C$26,E$4:E$26)</f>
         <v>0.0007207445205151251</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="6">
         <f>COVARIANCE.S(C$4:C$26,F$4:F$26)</f>
         <v>0.0010089856281822042</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="6">
         <f>COVARIANCE.S(C$4:C$26,G$4:G$26)</f>
         <v>0.0011780811272671613</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="6">
         <f>SUMPRODUCT(B34:G34,$B$30:$G$30)</f>
         <v>0.0011585726390565653</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="9">
         <f>C$30*H34*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>103737.12099213374</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="9">
         <f>I34/C$30</f>
         <v>576317.3388451874</v>
       </c>
-      <c r="K34" s="13">
+      <c r="K34" s="9">
         <f>C$30*STDEV.S(C$4:C$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>113263.98452945186</v>
       </c>
@@ -13977,43 +13921,43 @@
       <c r="A35" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="6">
         <f>COVARIANCE.S(D$4:D$26,B$4:B$26)</f>
         <v>0.001255970611206699</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="6">
         <f>COVARIANCE.S(D$4:D$26,C$4:C$26)</f>
         <v>0.0013546728920645023</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="6">
         <f>COVARIANCE.S(D$4:D$26,D$4:D$26)</f>
         <v>0.001673939806505305</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="6">
         <f>COVARIANCE.S(D$4:D$26,E$4:E$26)</f>
         <v>0.0008418844015922254</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="6">
         <f>COVARIANCE.S(D$4:D$26,F$4:F$26)</f>
         <v>0.0009422475139068253</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="6">
         <f>COVARIANCE.S(D$4:D$26,G$4:G$26)</f>
         <v>0.0014225041019277726</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="6">
         <f>SUMPRODUCT(B35:G35,$B$30:$G$30)</f>
         <v>0.0012481389963876</v>
       </c>
-      <c r="I35" s="13">
+      <c r="I35" s="9">
         <f>D$30*H35*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>99339.35888460213</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J35" s="9">
         <f>I35/D$30</f>
         <v>620870.9930287633</v>
       </c>
-      <c r="K35" s="13">
+      <c r="K35" s="9">
         <f>D$30*STDEV.S(D$4:D$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>107685.14656228223</v>
       </c>
@@ -14022,43 +13966,43 @@
       <c r="A36" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="6">
         <f>COVARIANCE.S(E$4:E$26,B$4:B$26)</f>
         <v>0.000678949334674663</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="6">
         <f>COVARIANCE.S(E$4:E$26,C$4:C$26)</f>
         <v>0.0007207445205151251</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="6">
         <f>COVARIANCE.S(E$4:E$26,D$4:D$26)</f>
         <v>0.0008418844015922254</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="6">
         <f>COVARIANCE.S(E$4:E$26,E$4:E$26)</f>
         <v>0.000528122670100409</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="6">
         <f>COVARIANCE.S(E$4:E$26,F$4:F$26)</f>
         <v>0.0006903472911133862</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="6">
         <f>COVARIANCE.S(E$4:E$26,G$4:G$26)</f>
         <v>0.0008074802628427954</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="6">
         <f>SUMPRODUCT(B36:G36,$B$30:$G$30)</f>
         <v>0.0007078908785461614</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="9">
         <f>E$30*H36*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>59862.33534764133</v>
       </c>
-      <c r="J36" s="13">
+      <c r="J36" s="9">
         <f>I36/E$30</f>
         <v>352131.38439789024</v>
       </c>
-      <c r="K36" s="13">
+      <c r="K36" s="9">
         <f>E$30*STDEV.S(E$4:E$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>64266.14193147077</v>
       </c>
@@ -14067,43 +14011,43 @@
       <c r="A37" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="6">
         <f>COVARIANCE.S(F$4:F$26,B$4:B$26)</f>
         <v>0.0010365458850546678</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="6">
         <f>COVARIANCE.S(F$4:F$26,C$4:C$26)</f>
         <v>0.0010089856281822042</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="6">
         <f>COVARIANCE.S(F$4:F$26,D$4:D$26)</f>
         <v>0.0009422475139068253</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="6">
         <f>COVARIANCE.S(F$4:F$26,E$4:E$26)</f>
         <v>0.0006903472911133862</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="6">
         <f>COVARIANCE.S(F$4:F$26,F$4:F$26)</f>
         <v>0.0011838956809813053</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="6">
         <f>COVARIANCE.S(F$4:F$26,G$4:G$26)</f>
         <v>0.0012238657330600076</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="6">
         <f>SUMPRODUCT(B37:G37,$B$30:$G$30)</f>
         <v>0.0010078439850537482</v>
       </c>
-      <c r="I37" s="13">
+      <c r="I37" s="9">
         <f>F$30*H37*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>75200.89080175663</v>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="9">
         <f>I37/F$30</f>
         <v>501339.2720117108</v>
       </c>
-      <c r="K37" s="13">
+      <c r="K37" s="9">
         <f>F$30*STDEV.S(F$4:F$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>84901.20993122969</v>
       </c>
@@ -14112,43 +14056,43 @@
       <c r="A38" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="6">
         <f>COVARIANCE.S(G$4:G$26,B$4:B$26)</f>
         <v>0.0014133312018288144</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="6">
         <f>COVARIANCE.S(G$4:G$26,C$4:C$26)</f>
         <v>0.0011780811272671613</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="6">
         <f>COVARIANCE.S(G$4:G$26,D$4:D$26)</f>
         <v>0.0014225041019277726</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="6">
         <f>COVARIANCE.S(G$4:G$26,E$4:E$26)</f>
         <v>0.0008074802628427954</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="6">
         <f>COVARIANCE.S(G$4:G$26,F$4:F$26)</f>
         <v>0.0012238657330600076</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="6">
         <f>COVARIANCE.S(G$4:G$26,G$4:G$26)</f>
         <v>0.0017645284907911445</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="6">
         <f>SUMPRODUCT(B38:G38,$B$30:$G$30)</f>
         <v>0.0012937189658249555</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="9">
         <f>G$30*H38*'参数设置'!$B$3*'参数设置'!$B$7/SQRT($B$41)</f>
         <v>96531.62604525105</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="9">
         <f>I38/G$30</f>
         <v>643544.1736350069</v>
       </c>
-      <c r="K38" s="13">
+      <c r="K38" s="9">
         <f>G$30*STDEV.S(G$4:G$26)*'参数设置'!$B$3*'参数设置'!$B$7</f>
         <v>103650.52325439315</v>
       </c>
@@ -14157,7 +14101,7 @@
       <c r="A41" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="6">
         <f>B30*H33+C30*H34+D30*H35+E30*H36+F30*H37+G30*H38</f>
         <v>0.001093591104446019</v>
       </c>
@@ -14166,7 +14110,7 @@
       <c r="A42" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="9">
         <f>SQRT(B41)*'参数设置'!B3*'参数设置'!B7</f>
         <v>543993.0944790144</v>
       </c>
@@ -14175,7 +14119,7 @@
       <c r="A43" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="9">
         <f>SUM(I33:I38)</f>
         <v>543993.0944790144</v>
       </c>
@@ -14184,7 +14128,7 @@
       <c r="A44" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="9">
         <f>SUM(K33:K38)-B42</f>
         <v>44714.50707774027</v>
       </c>
@@ -14193,7 +14137,7 @@
       <c r="A45" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="16" t="str">
+      <c r="B45" s="5" t="str">
         <f>INDEX(A33:A38,MATCH(MAX(I33:I38),I33:I38,0))</f>
         <v>科技</v>
       </c>
@@ -14289,46 +14233,46 @@
       <c r="A4" s="3">
         <v>45716</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <f>'月度收益'!O14</f>
         <v>-0.02857961496630279</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <f>STDEV.S('月度收益'!O2:O13)*SQRT(12)</f>
         <v>0.10483841241923837</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="6">
         <f>SLOPE('月度收益'!O2:O13,'月度收益'!N2:N13)</f>
         <v>1.015946486762296</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <f>STDEV.S($O$4:$O$15)*SQRT(12)</f>
         <v>0.006498450214483079</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <f>MAX(0,-SMALL('月度收益'!O2:O13,2))</f>
         <v>0.012866339018591872</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O2:O13,1),SMALL('月度收益'!O2:O13,2)))</f>
         <v>0.02610491021506569</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="6">
         <f>IF(B4&lt;-F4,1,0)</f>
         <v>1</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="6">
         <f>AVERAGE($O$4:$O$15)*12/E4</f>
         <v>9.264631633450582</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <f>MAX(0,-B4)</f>
         <v>0.02857961496630279</v>
       </c>
       <c r="N4" s="3">
         <v>45351</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="10">
         <f>'月度收益'!O2-'月度收益'!N2</f>
         <v>0.007824327253655068</v>
       </c>
@@ -14337,46 +14281,46 @@
       <c r="A5" s="3">
         <v>45747</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <f>'月度收益'!O15</f>
         <v>-0.02817391571200374</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <f>STDEV.S('月度收益'!O3:O14)*SQRT(12)</f>
         <v>0.11065526195536365</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="6">
         <f>SLOPE('月度收益'!O3:O14,'月度收益'!N3:N14)</f>
         <v>1.0160922076307974</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <f>STDEV.S($O$5:$O$16)*SQRT(12)</f>
         <v>0.006091175813931428</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <f>MAX(0,-SMALL('月度收益'!O3:O14,2))</f>
         <v>0.02857961496630279</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O3:O14,1),SMALL('月度收益'!O3:O14,2)))</f>
         <v>0.03396154818892115</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="6">
         <f>IF(B5&lt;-F5,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="6">
         <f>AVERAGE($O$5:$O$16)*12/E5</f>
         <v>9.042857600384956</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <f>MAX(0,-B5)</f>
         <v>0.02817391571200374</v>
       </c>
       <c r="N5" s="3">
         <v>45382</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <f>'月度收益'!O3-'月度收益'!N3</f>
         <v>0.004699684832690211</v>
       </c>
@@ -14385,46 +14329,46 @@
       <c r="A6" s="3">
         <v>45777</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <f>'月度收益'!O16</f>
         <v>-0.06571119226883793</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <f>STDEV.S('月度收益'!O4:O15)*SQRT(12)</f>
         <v>0.11422690277540343</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="6">
         <f>SLOPE('月度收益'!O4:O15,'月度收益'!N4:N15)</f>
         <v>1.0285783366770354</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <f>STDEV.S($O$6:$O$17)*SQRT(12)</f>
         <v>0.00801960584215832</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>MAX(0,-SMALL('月度收益'!O4:O15,2))</f>
         <v>0.02857961496630279</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O4:O15,1),SMALL('月度收益'!O4:O15,2)))</f>
         <v>0.03396154818892115</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="6">
         <f>IF(B6&lt;-F6,1,0)</f>
         <v>1</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="6">
         <f>AVERAGE($O$6:$O$17)*12/E6</f>
         <v>6.202833536449956</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <f>MAX(0,-B6)</f>
         <v>0.06571119226883793</v>
       </c>
       <c r="N6" s="3">
         <v>45412</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <f>'月度收益'!O4-'月度收益'!N4</f>
         <v>0.0022071910823286515</v>
       </c>
@@ -14433,46 +14377,46 @@
       <c r="A7" s="3">
         <v>45808</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <f>'月度收益'!O17</f>
         <v>0.01990953804549747</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <f>STDEV.S('月度收益'!O5:O16)*SQRT(12)</f>
         <v>0.1336380507168803</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="6">
         <f>SLOPE('月度收益'!O5:O16,'月度收益'!N5:N16)</f>
         <v>1.04673088324702</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <f>STDEV.S($O$7:$O$18)*SQRT(12)</f>
         <v>0.009754441291845594</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f>MAX(0,-SMALL('月度收益'!O5:O16,2))</f>
         <v>0.0393434814115395</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O5:O16,1),SMALL('月度收益'!O5:O16,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="6">
         <f>IF(B7&lt;-F7,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="6">
         <f>AVERAGE($O$7:$O$18)*12/E7</f>
         <v>4.707270425713751</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <f>MAX(0,-B7)</f>
         <v>0</v>
       </c>
       <c r="N7" s="3">
         <v>45443</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <f>'月度收益'!O5-'月度收益'!N5</f>
         <v>0.0015677445252054783</v>
       </c>
@@ -14481,46 +14425,46 @@
       <c r="A8" s="3">
         <v>45838</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <f>'月度收益'!O18</f>
         <v>0.043947961278318</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f>STDEV.S('月度收益'!O6:O17)*SQRT(12)</f>
         <v>0.13532638138870484</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="6">
         <f>SLOPE('月度收益'!O6:O17,'月度收益'!N6:N17)</f>
         <v>1.0476691231338255</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <f>STDEV.S($O$8:$O$19)*SQRT(12)</f>
         <v>0.009541657770926753</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>MAX(0,-SMALL('月度收益'!O6:O17,2))</f>
         <v>0.0393434814115395</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O6:O17,1),SMALL('月度收益'!O6:O17,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="6">
         <f>IF(B8&lt;-F8,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="6">
         <f>AVERAGE($O$8:$O$19)*12/E8</f>
         <v>5.217404301783672</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <f>MAX(0,-B8)</f>
         <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>45473</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="10">
         <f>'月度收益'!O6-'月度收益'!N6</f>
         <v>0.00715242120426128</v>
       </c>
@@ -14529,46 +14473,46 @@
       <c r="A9" s="3">
         <v>45869</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <f>'月度收益'!O19</f>
         <v>0.04226941513310616</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f>STDEV.S('月度收益'!O7:O18)*SQRT(12)</f>
         <v>0.1420188468336544</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="6">
         <f>SLOPE('月度收益'!O7:O18,'月度收益'!N7:N18)</f>
         <v>1.0630018986628158</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <f>STDEV.S($O$9:$O$20)*SQRT(12)</f>
         <v>0.012564155213800067</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f>MAX(0,-SMALL('月度收益'!O7:O18,2))</f>
         <v>0.0393434814115395</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O7:O18,1),SMALL('月度收益'!O7:O18,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="6">
         <f>IF(B9&lt;-F9,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="6">
         <f>AVERAGE($O$9:$O$20)*12/E9</f>
         <v>4.402378630799633</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <f>MAX(0,-B9)</f>
         <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>45504</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="10">
         <f>'月度收益'!O7-'月度收益'!N7</f>
         <v>0.004631371038258454</v>
       </c>
@@ -14577,46 +14521,46 @@
       <c r="A10" s="3">
         <v>45900</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <f>'月度收益'!O20</f>
         <v>0.0276081557207723</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <f>STDEV.S('月度收益'!O8:O19)*SQRT(12)</f>
         <v>0.14685936596862115</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="6">
         <f>SLOPE('月度收益'!O8:O19,'月度收益'!N8:N19)</f>
         <v>1.0666734740893153</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <f>STDEV.S($O$10:$O$21)*SQRT(12)</f>
         <v>0.013229733518517297</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f>MAX(0,-SMALL('月度收益'!O8:O19,2))</f>
         <v>0.0393434814115395</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O8:O19,1),SMALL('月度收益'!O8:O19,2)))</f>
         <v>0.05252733684018872</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="6">
         <f>IF(B10&lt;-F10,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="6">
         <f>AVERAGE($O$10:$O$21)*12/E10</f>
         <v>4.492276654027392</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <f>MAX(0,-B10)</f>
         <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>45535</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="10">
         <f>'月度收益'!O8-'月度收益'!N8</f>
         <v>0.0035878284926138884</v>
       </c>
@@ -14625,46 +14569,46 @@
       <c r="A11" s="3">
         <v>45930</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <f>'月度收益'!O21</f>
         <v>0.05249246842142453</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f>STDEV.S('月度收益'!O9:O20)*SQRT(12)</f>
         <v>0.13844296359137812</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="6">
         <f>SLOPE('月度收益'!O9:O20,'月度收益'!N9:N20)</f>
         <v>1.0720413057505451</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f>STDEV.S($O$11:$O$22)*SQRT(12)</f>
         <v>0.013169956602410356</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f>MAX(0,-SMALL('月度收益'!O9:O20,2))</f>
         <v>0.02857961496630279</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O9:O20,1),SMALL('月度收益'!O9:O20,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="6">
         <f>IF(B11&lt;-F11,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="6">
         <f>AVERAGE($O$11:$O$22)*12/E11</f>
         <v>4.686399089334704</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <f>MAX(0,-B11)</f>
         <v>0</v>
       </c>
       <c r="N11" s="3">
         <v>45565</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="10">
         <f>'月度收益'!O9-'月度收益'!N9</f>
         <v>0.006099553428397603</v>
       </c>
@@ -14673,46 +14617,46 @@
       <c r="A12" s="3">
         <v>45961</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <f>'月度收益'!O22</f>
         <v>-0.006462350335248799</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f>STDEV.S('月度收益'!O10:O21)*SQRT(12)</f>
         <v>0.14251929528228524</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="6">
         <f>SLOPE('月度收益'!O10:O21,'月度收益'!N10:N21)</f>
         <v>1.0615046649827529</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <f>STDEV.S($O$12:$O$23)*SQRT(12)</f>
         <v>0.013230294672924662</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <f>MAX(0,-SMALL('月度收益'!O10:O21,2))</f>
         <v>0.02857961496630279</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O10:O21,1),SMALL('月度收益'!O10:O21,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="6">
         <f>IF(B12&lt;-F12,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="6">
         <f>AVERAGE($O$12:$O$23)*12/E12</f>
         <v>4.462415202672049</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f>MAX(0,-B12)</f>
         <v>0.006462350335248799</v>
       </c>
       <c r="N12" s="3">
         <v>45596</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="10">
         <f>'月度收益'!O10-'月度收益'!N10</f>
         <v>0.004779616881047569</v>
       </c>
@@ -14721,46 +14665,46 @@
       <c r="A13" s="3">
         <v>45991</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <f>'月度收益'!O23</f>
         <v>-0.005440672089627106</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f>STDEV.S('月度收益'!O11:O22)*SQRT(12)</f>
         <v>0.14121341961734585</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="6">
         <f>SLOPE('月度收益'!O11:O22,'月度收益'!N11:N22)</f>
         <v>1.0661535884572453</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <f>STDEV.S($O$13:$O$24)*SQRT(12)</f>
         <v>0.01355118941402172</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <f>MAX(0,-SMALL('月度收益'!O11:O22,2))</f>
         <v>0.02857961496630279</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O11:O22,1),SMALL('月度收益'!O11:O22,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="6">
         <f>IF(B13&lt;-F13,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="6">
         <f>AVERAGE($O$13:$O$24)*12/E13</f>
         <v>4.151412468168613</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <f>MAX(0,-B13)</f>
         <v>0.005440672089627106</v>
       </c>
       <c r="N13" s="3">
         <v>45626</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="10">
         <f>'月度收益'!O11-'月度收益'!N11</f>
         <v>0.0056393084059468</v>
       </c>
@@ -14769,46 +14713,46 @@
       <c r="A14" s="3">
         <v>46022</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <f>'月度收益'!O24</f>
         <v>0.007554182370882454</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f>STDEV.S('月度收益'!O12:O23)*SQRT(12)</f>
         <v>0.1223065066275717</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="6">
         <f>SLOPE('月度收益'!O12:O23,'月度收益'!N12:N23)</f>
         <v>1.0870556443068415</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <f>STDEV.S($O$14:$O$25)*SQRT(12)</f>
         <v>0.013603508315537008</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="10">
         <f>MAX(0,-SMALL('月度收益'!O12:O23,2))</f>
         <v>0.02857961496630279</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <f>MAX(0,-AVERAGE(SMALL('月度收益'!O12:O23,1),SMALL('月度收益'!O12:O23,2)))</f>
         <v>0.04714540361757036</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="6">
         <f>IF(B14&lt;-F14,1,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="6">
         <f>AVERAGE($O$14:$O$25)*12/E14</f>
         <v>3.942987023247805</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <f>MAX(0,-B14)</f>
         <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>45657</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="10">
         <f>'月度收益'!O12-'月度收益'!N12</f>
         <v>0.0065579776955535865</v>
       </c>
@@ -14817,7 +14761,7 @@
       <c r="N15" s="3">
         <v>45688</v>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="10">
         <f>'月度收益'!O13-'月度收益'!N13</f>
         <v>0.0054587225855450665</v>
       </c>
@@ -14826,7 +14770,7 @@
       <c r="N16" s="3">
         <v>45716</v>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="10">
         <f>'月度收益'!O14-'月度收益'!N14</f>
         <v>0.002700215332442246</v>
       </c>
@@ -14835,14 +14779,14 @@
       <c r="A17" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="6">
         <f>SUM(H4:H14)</f>
         <v>2</v>
       </c>
       <c r="N17" s="3">
         <v>45747</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="10">
         <f>'月度收益'!O15-'月度收益'!N15</f>
         <v>-0.00063767060475102</v>
       </c>
@@ -14851,14 +14795,14 @@
       <c r="A18" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <f>B17/COUNT(B4:B14)</f>
         <v>0.18181818181818182</v>
       </c>
       <c r="N18" s="3">
         <v>45777</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="10">
         <f>'月度收益'!O16-'月度收益'!N16</f>
         <v>-0.0016202959720551524</v>
       </c>
@@ -14867,14 +14811,14 @@
       <c r="A19" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="6">
         <f>COUNT(B4:B14)*10%</f>
         <v>1.1</v>
       </c>
       <c r="N19" s="3">
         <v>45808</v>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="10">
         <f>'月度收益'!O17-'月度收益'!N17</f>
         <v>0.005433637812920528</v>
       </c>
@@ -14883,14 +14827,14 @@
       <c r="A20" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="16" t="str">
+      <c r="B20" s="5" t="str">
         <f>IF(B17&lt;=2,"正常","复核")</f>
         <v>正常</v>
       </c>
       <c r="N20" s="3">
         <v>45838</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="10">
         <f>'月度收益'!O18-'月度收益'!N18</f>
         <v>0.01268190333136364</v>
       </c>
@@ -14899,7 +14843,7 @@
       <c r="N21" s="3">
         <v>45869</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="10">
         <f>'月度收益'!O19-'月度收益'!N19</f>
         <v>0.00875082563521417</v>
       </c>
@@ -14908,7 +14852,7 @@
       <c r="N22" s="3">
         <v>45900</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="10">
         <f>'月度收益'!O20-'月度收益'!N20</f>
         <v>0.005875878096488429</v>
       </c>
@@ -14917,7 +14861,7 @@
       <c r="N23" s="3">
         <v>45930</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="10">
         <f>'月度收益'!O21-'月度收益'!N21</f>
         <v>0.003418948884574176</v>
       </c>
@@ -14926,7 +14870,7 @@
       <c r="N24" s="3">
         <v>45961</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="10">
         <f>'月度收益'!O22-'月度收益'!N22</f>
         <v>0.0019971254886418177</v>
       </c>
@@ -14935,7 +14879,7 @@
       <c r="N25" s="3">
         <v>45991</v>
       </c>
-      <c r="O25" s="11">
+      <c r="O25" s="10">
         <f>'月度收益'!O23-'月度收益'!N23</f>
         <v>0.003021188472868543</v>
       </c>
@@ -14944,7 +14888,7 @@
       <c r="N26" s="3">
         <v>46022</v>
       </c>
-      <c r="O26" s="11">
+      <c r="O26" s="10">
         <f>'月度收益'!O24-'月度收益'!N24</f>
         <v>0.0038502179852477588</v>
       </c>
